--- a/Python/Thingiverse/model_stats.xlsx
+++ b/Python/Thingiverse/model_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Thingiverse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11AB1550-20FB-413E-ABD0-78257F1A5803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E9C4E2-ABA6-4FBC-85D3-9AA6DE276AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Mammoth</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t>QMJHL</t>
-  </si>
-  <si>
-    <t>Team</t>
   </si>
   <si>
     <t>Views</t>
@@ -111,7 +108,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>tat</t>
+    <t>Model</t>
   </si>
 </sst>
 </file>
@@ -119,7 +116,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -155,41 +152,41 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -211,14 +208,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V19" totalsRowShown="0">
-  <autoFilter ref="A1:V19" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V25" totalsRowShown="0">
+  <autoFilter ref="A1:V25" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
   <tableColumns count="22">
     <tableColumn id="22" xr3:uid="{B838C6CD-92E8-4070-81DB-2EDE900509A2}" name="Date"/>
-    <tableColumn id="1" xr3:uid="{C06BFB11-D5FB-45F8-853C-B38F6CA36FF6}" name="Team"/>
+    <tableColumn id="1" xr3:uid="{C06BFB11-D5FB-45F8-853C-B38F6CA36FF6}" name="Model"/>
     <tableColumn id="13" xr3:uid="{AEE26F58-911F-4534-94C6-8FCA31D6F4B1}" name="Published"/>
     <tableColumn id="14" xr3:uid="{11FE9DF7-F747-41F2-BE31-8FAB66C0B838}" name="Age" dataDxfId="11">
-      <calculatedColumnFormula>NOW()-Table1[[#This Row],[Published]]</calculatedColumnFormula>
+      <calculatedColumnFormula>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{7E393A08-4718-4CB8-8F50-8ACBD51A470F}" name="Views" dataDxfId="10"/>
     <tableColumn id="3" xr3:uid="{AE7E7C79-96E4-4AA4-8ABE-36217F4A6424}" name="Downloads"/>
@@ -560,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC85C3B-1FD4-46FE-8A2F-07E281673B93}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -589,70 +586,70 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="W1"/>
     </row>
@@ -667,8 +664,8 @@
         <v>45784</v>
       </c>
       <c r="D2" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>291.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>278</v>
       </c>
       <c r="E2" s="3">
         <v>658</v>
@@ -707,28 +704,28 @@
         <v>7.5987841945288756E-3</v>
       </c>
       <c r="P2" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>2.2560862281528107</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3669064748201438</v>
       </c>
       <c r="Q2" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.49030445383868076</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.51438848920863312</v>
       </c>
       <c r="R2" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>3.7715727218360057E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.9568345323741004E-2</v>
       </c>
       <c r="S2" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
-        <v>1.7143512371981844E-2</v>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.7985611510791366E-2</v>
       </c>
       <c r="T2" s="4">
         <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
         <v>997</v>
       </c>
       <c r="U2" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>3.41841636697318</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5863309352517985</v>
       </c>
       <c r="V2" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -747,8 +744,8 @@
         <v>45785</v>
       </c>
       <c r="D3" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>290.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>277</v>
       </c>
       <c r="E3" s="3">
         <v>307</v>
@@ -787,19 +784,19 @@
         <v>0</v>
       </c>
       <c r="P3" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>1.056233168919499</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1083032490974729</v>
       </c>
       <c r="Q3" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.27523991372495088</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.28880866425992779</v>
       </c>
       <c r="R3" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>1.3761995686247546E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.444043321299639E-2</v>
       </c>
       <c r="S3" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T3" s="4">
@@ -807,8 +804,8 @@
         <v>479</v>
       </c>
       <c r="U3" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>1.6479989834281437</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.7292418772563176</v>
       </c>
       <c r="V3" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -827,8 +824,8 @@
         <v>45930</v>
       </c>
       <c r="D4" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>145.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>132</v>
       </c>
       <c r="E4" s="3">
         <v>206</v>
@@ -867,19 +864,19 @@
         <v>0</v>
       </c>
       <c r="P4" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>1.4142958761658759</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5606060606060606</v>
       </c>
       <c r="Q4" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.56983765884353255</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.62878787878787878</v>
       </c>
       <c r="R4" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>3.4327569809851355E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.787878787878788E-2</v>
       </c>
       <c r="S4" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T4" s="4">
@@ -887,8 +884,8 @@
         <v>387</v>
       </c>
       <c r="U4" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>2.6569539032824947</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9318181818181817</v>
       </c>
       <c r="V4" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -901,14 +898,14 @@
         <v>46062</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1">
         <v>45750</v>
       </c>
       <c r="D5" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>325.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>312</v>
       </c>
       <c r="E5" s="3">
         <v>150</v>
@@ -947,28 +944,28 @@
         <v>6.6666666666666671E-3</v>
       </c>
       <c r="P5" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>0.46060942070267502</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.48076923076923078</v>
       </c>
       <c r="Q5" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>7.676823678377917E-2</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.0128205128205135E-2</v>
       </c>
       <c r="R5" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>6.1414589427023335E-3</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.41025641025641E-3</v>
       </c>
       <c r="S5" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
-        <v>3.0707294713511668E-3</v>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.205128205128205E-3</v>
       </c>
       <c r="T5" s="4">
         <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
         <v>210</v>
       </c>
       <c r="U5" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>0.644853188983745</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.67307692307692313</v>
       </c>
       <c r="V5" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -987,8 +984,8 @@
         <v>45932</v>
       </c>
       <c r="D6" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>143.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>130</v>
       </c>
       <c r="E6" s="3">
         <v>97</v>
@@ -1027,19 +1024,19 @@
         <v>0</v>
       </c>
       <c r="P6" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>0.67522640696006697</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.74615384615384617</v>
       </c>
       <c r="Q6" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>7.6572066768667388E-2</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.461538461538462E-2</v>
       </c>
       <c r="R6" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>6.9610969789697628E-3</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.6923076923076927E-3</v>
       </c>
       <c r="S6" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T6" s="4">
@@ -1047,8 +1044,8 @@
         <v>122</v>
       </c>
       <c r="U6" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>0.8492538314343111</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.93846153846153846</v>
       </c>
       <c r="V6" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1067,8 +1064,8 @@
         <v>46034</v>
       </c>
       <c r="D7" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>41.655519097221259</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>28</v>
       </c>
       <c r="E7" s="3">
         <v>79</v>
@@ -1107,19 +1104,19 @@
         <v>0</v>
       </c>
       <c r="P7" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>1.8965073947492808</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.8214285714285716</v>
       </c>
       <c r="Q7" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.57615414524028785</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.8571428571428571</v>
       </c>
       <c r="R7" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>4.8012845436690654E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="S7" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T7" s="4">
@@ -1127,8 +1124,8 @@
         <v>133</v>
       </c>
       <c r="U7" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>3.1928542215399283</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>4.75</v>
       </c>
       <c r="V7" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1147,8 +1144,8 @@
         <v>45784</v>
       </c>
       <c r="D8" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>291.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>283</v>
       </c>
       <c r="E8" s="3">
         <v>688</v>
@@ -1187,28 +1184,28 @@
         <v>7.2674418604651162E-3</v>
       </c>
       <c r="P8" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>2.3589473023847018</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.431095406360424</v>
       </c>
       <c r="Q8" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.50059056126186985</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.51590106007067138</v>
       </c>
       <c r="R8" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>4.1144429692756432E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.2402826855123678E-2</v>
       </c>
       <c r="S8" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
-        <v>1.7143512371981844E-2</v>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.7667844522968199E-2</v>
       </c>
       <c r="T8" s="4">
         <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
         <v>1036</v>
       </c>
       <c r="U8" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>3.5521357634746384</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.6607773851590104</v>
       </c>
       <c r="V8" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1226,8 +1223,8 @@
         <v>45785</v>
       </c>
       <c r="D9" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>290.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>282</v>
       </c>
       <c r="E9" s="3">
         <v>310</v>
@@ -1266,19 +1263,19 @@
         <v>0</v>
       </c>
       <c r="P9" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>1.0665546656841847</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0992907801418439</v>
       </c>
       <c r="Q9" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.27523991372495088</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.28368794326241137</v>
       </c>
       <c r="R9" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>1.3761995686247546E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4184397163120567E-2</v>
       </c>
       <c r="S9" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T9" s="4">
@@ -1286,8 +1283,8 @@
         <v>482</v>
       </c>
       <c r="U9" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>1.6583204801928293</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.7092198581560283</v>
       </c>
       <c r="V9" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1305,8 +1302,8 @@
         <v>45930</v>
       </c>
       <c r="D10" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>145.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>137</v>
       </c>
       <c r="E10" s="3">
         <v>207</v>
@@ -1345,19 +1342,19 @@
         <v>0</v>
       </c>
       <c r="P10" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>1.4211613901278461</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5109489051094891</v>
       </c>
       <c r="Q10" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.57670317280550276</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.61313868613138689</v>
       </c>
       <c r="R10" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>3.4327569809851355E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.6496350364963501E-2</v>
       </c>
       <c r="S10" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T10" s="4">
@@ -1365,8 +1362,8 @@
         <v>390</v>
       </c>
       <c r="U10" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>2.6775504451684058</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.8467153284671531</v>
       </c>
       <c r="V10" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1378,14 +1375,14 @@
         <v>46067</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1">
         <v>45750</v>
       </c>
       <c r="D11" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>325.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>317</v>
       </c>
       <c r="E11" s="3">
         <v>153</v>
@@ -1424,28 +1421,28 @@
         <v>6.5359477124183009E-3</v>
       </c>
       <c r="P11" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>0.46982160911672849</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.48264984227129337</v>
       </c>
       <c r="Q11" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>7.9838966255130331E-2</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.2018927444794956E-2</v>
       </c>
       <c r="R11" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>6.1414589427023335E-3</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.3091482649842269E-3</v>
       </c>
       <c r="S11" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
-        <v>3.0707294713511668E-3</v>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.1545741324921135E-3</v>
       </c>
       <c r="T11" s="4">
         <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
         <v>215</v>
       </c>
       <c r="U11" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>0.66020683634050081</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.67823343848580442</v>
       </c>
       <c r="V11" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1463,8 +1460,8 @@
         <v>45932</v>
       </c>
       <c r="D12" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>143.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>135</v>
       </c>
       <c r="E12" s="3">
         <v>105</v>
@@ -1503,19 +1500,19 @@
         <v>0</v>
       </c>
       <c r="P12" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>0.7309151827918251</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.77777777777777779</v>
       </c>
       <c r="Q12" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>7.6572066768667388E-2</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.1481481481481488E-2</v>
       </c>
       <c r="R12" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>6.9610969789697628E-3</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="S12" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T12" s="4">
@@ -1523,8 +1520,8 @@
         <v>130</v>
       </c>
       <c r="U12" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>0.90494260726606923</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.96296296296296291</v>
       </c>
       <c r="V12" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1542,8 +1539,8 @@
         <v>46034</v>
       </c>
       <c r="D13" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>41.655519097221259</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>33</v>
       </c>
       <c r="E13" s="3">
         <v>80</v>
@@ -1582,27 +1579,28 @@
         <v>0</v>
       </c>
       <c r="P13" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>1.9205138174676262</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.4242424242424243</v>
       </c>
       <c r="Q13" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.57615414524028785</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.72727272727272729</v>
       </c>
       <c r="R13" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>4.8012845436690654E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="S13" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T13" s="4">
         <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
         <v>134</v>
       </c>
-      <c r="U13" s="4" t="s">
-        <v>28</v>
+      <c r="U13" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>4.0606060606060606</v>
       </c>
       <c r="V13" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1620,8 +1618,8 @@
         <v>45784</v>
       </c>
       <c r="D14" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>291.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>291</v>
       </c>
       <c r="E14" s="3">
         <v>677</v>
@@ -1660,28 +1658,28 @@
         <v>7.385524372230428E-3</v>
       </c>
       <c r="P14" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>2.3212315751663417</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3264604810996565</v>
       </c>
       <c r="Q14" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.51773407363385171</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.51890034364261173</v>
       </c>
       <c r="R14" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>4.1144429692756432E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.1237113402061855E-2</v>
       </c>
       <c r="S14" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
-        <v>1.7143512371981844E-2</v>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.7182130584192441E-2</v>
       </c>
       <c r="T14" s="4">
         <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
         <v>1035</v>
       </c>
       <c r="U14" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>3.548707061000242</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5567010309278349</v>
       </c>
       <c r="V14" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1699,8 +1697,8 @@
         <v>45785</v>
       </c>
       <c r="D15" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>290.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>290</v>
       </c>
       <c r="E15" s="3">
         <v>316</v>
@@ -1739,19 +1737,19 @@
         <v>0</v>
       </c>
       <c r="P15" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>1.0871976592135562</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0896551724137931</v>
       </c>
       <c r="Q15" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.28212091156807467</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.28275862068965518</v>
       </c>
       <c r="R15" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>1.3761995686247546E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3793103448275862E-2</v>
       </c>
       <c r="S15" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T15" s="4">
@@ -1759,8 +1757,8 @@
         <v>492</v>
       </c>
       <c r="U15" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>1.6927254694084481</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6965517241379311</v>
       </c>
       <c r="V15" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1778,8 +1776,8 @@
         <v>45930</v>
       </c>
       <c r="D16" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>145.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>145</v>
       </c>
       <c r="E16" s="3">
         <v>217</v>
@@ -1818,19 +1816,19 @@
         <v>0</v>
       </c>
       <c r="P16" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>1.4898165297475487</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4965517241379311</v>
       </c>
       <c r="Q16" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.60416522865338385</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.60689655172413792</v>
       </c>
       <c r="R16" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>3.4327569809851355E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.4482758620689655E-2</v>
       </c>
       <c r="S16" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T16" s="4">
@@ -1838,8 +1836,8 @@
         <v>408</v>
       </c>
       <c r="U16" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>2.8011296964838706</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.8137931034482757</v>
       </c>
       <c r="V16" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1851,14 +1849,14 @@
         <v>46075</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>45750</v>
       </c>
       <c r="D17" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>325.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>325</v>
       </c>
       <c r="E17" s="3">
         <v>154</v>
@@ -1897,28 +1895,28 @@
         <v>6.4935064935064939E-3</v>
       </c>
       <c r="P17" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>0.47289233858807966</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.47384615384615386</v>
       </c>
       <c r="Q17" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>8.2909695726481505E-2</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.3076923076923076E-2</v>
       </c>
       <c r="R17" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>6.1414589427023335E-3</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.1538461538461538E-3</v>
       </c>
       <c r="S17" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
-        <v>3.0707294713511668E-3</v>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.0769230769230769E-3</v>
       </c>
       <c r="T17" s="4">
         <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
         <v>218</v>
       </c>
       <c r="U17" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>0.66941902475455428</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.67076923076923078</v>
       </c>
       <c r="V17" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -1936,8 +1934,8 @@
         <v>45932</v>
       </c>
       <c r="D18" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>143.65551909722126</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>143</v>
       </c>
       <c r="E18" s="3">
         <v>116</v>
@@ -1976,19 +1974,19 @@
         <v>0</v>
       </c>
       <c r="P18" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>0.80748724956049256</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.81118881118881114</v>
       </c>
       <c r="Q18" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>7.6572066768667388E-2</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>7.6923076923076927E-2</v>
       </c>
       <c r="R18" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>6.9610969789697628E-3</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.993006993006993E-3</v>
       </c>
       <c r="S18" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T18" s="4">
@@ -1996,8 +1994,8 @@
         <v>141</v>
       </c>
       <c r="U18" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>0.98151467403473658</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.98601398601398604</v>
       </c>
       <c r="V18" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
@@ -2015,8 +2013,8 @@
         <v>46034</v>
       </c>
       <c r="D19" s="2">
-        <f ca="1">NOW()-Table1[[#This Row],[Published]]</f>
-        <v>41.655519097221259</v>
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>41</v>
       </c>
       <c r="E19" s="3">
         <v>85</v>
@@ -2055,19 +2053,19 @@
         <v>0</v>
       </c>
       <c r="P19" s="4">
-        <f ca="1">Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
-        <v>2.0405459310593526</v>
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.0731707317073171</v>
       </c>
       <c r="Q19" s="4">
-        <f ca="1">Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
-        <v>0.57615414524028785</v>
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.58536585365853655</v>
       </c>
       <c r="R19" s="4">
-        <f ca="1">Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
-        <v>4.8012845436690654E-2</v>
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.878048780487805E-2</v>
       </c>
       <c r="S19" s="4">
-        <f ca="1">Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
         <v>0</v>
       </c>
       <c r="T19" s="4">
@@ -2075,16 +2073,562 @@
         <v>139</v>
       </c>
       <c r="U19" s="4">
-        <f ca="1">Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
-        <v>3.3368927578500003</v>
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.3902439024390243</v>
       </c>
       <c r="V19" s="4">
         <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
         <v>1.6352941176470588</v>
       </c>
     </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D20" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>297</v>
+      </c>
+      <c r="E20" s="3">
+        <v>693</v>
+      </c>
+      <c r="F20">
+        <v>158</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.227994227994228</v>
+      </c>
+      <c r="N20" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7316017316017316E-2</v>
+      </c>
+      <c r="O20" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>7.215007215007215E-3</v>
+      </c>
+      <c r="P20" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="Q20" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.53198653198653201</v>
+      </c>
+      <c r="R20" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.0404040404040407E-2</v>
+      </c>
+      <c r="S20" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6835016835016835E-2</v>
+      </c>
+      <c r="T20" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1065</v>
+      </c>
+      <c r="U20" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5858585858585861</v>
+      </c>
+      <c r="V20" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5367965367965368</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D21" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>296</v>
+      </c>
+      <c r="E21" s="3">
+        <v>328</v>
+      </c>
+      <c r="F21">
+        <v>85</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.25914634146341464</v>
+      </c>
+      <c r="N21" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2195121951219513E-2</v>
+      </c>
+      <c r="O21" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1081081081081081</v>
+      </c>
+      <c r="Q21" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.28716216216216217</v>
+      </c>
+      <c r="R21" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3513513513513514E-2</v>
+      </c>
+      <c r="S21" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T21" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>510</v>
+      </c>
+      <c r="U21" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.722972972972973</v>
+      </c>
+      <c r="V21" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5548780487804879</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D22" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>151</v>
+      </c>
+      <c r="E22" s="3">
+        <v>226</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.44247787610619471</v>
+      </c>
+      <c r="N22" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2123893805309734E-2</v>
+      </c>
+      <c r="O22" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4966887417218544</v>
+      </c>
+      <c r="Q22" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.66225165562913912</v>
+      </c>
+      <c r="R22" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.3112582781456956E-2</v>
+      </c>
+      <c r="S22" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T22" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>441</v>
+      </c>
+      <c r="U22" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9205298013245033</v>
+      </c>
+      <c r="V22" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9513274336283186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D23" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>331</v>
+      </c>
+      <c r="E23" s="3">
+        <v>164</v>
+      </c>
+      <c r="F23">
+        <v>29</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.17682926829268292</v>
+      </c>
+      <c r="N23" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8292682926829267E-2</v>
+      </c>
+      <c r="O23" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2195121951219513E-2</v>
+      </c>
+      <c r="P23" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.49546827794561932</v>
+      </c>
+      <c r="Q23" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.7613293051359523E-2</v>
+      </c>
+      <c r="R23" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>9.0634441087613302E-3</v>
+      </c>
+      <c r="S23" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>6.0422960725075529E-3</v>
+      </c>
+      <c r="T23" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>239</v>
+      </c>
+      <c r="U23" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.72205438066465255</v>
+      </c>
+      <c r="V23" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4573170731707317</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D24" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>149</v>
+      </c>
+      <c r="E24" s="3">
+        <v>123</v>
+      </c>
+      <c r="F24">
+        <v>12</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>9.7560975609756101E-2</v>
+      </c>
+      <c r="N24" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>8.130081300813009E-3</v>
+      </c>
+      <c r="O24" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>8.130081300813009E-3</v>
+      </c>
+      <c r="P24" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.82550335570469802</v>
+      </c>
+      <c r="Q24" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.0536912751677847E-2</v>
+      </c>
+      <c r="R24" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.7114093959731542E-3</v>
+      </c>
+      <c r="S24" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>6.7114093959731542E-3</v>
+      </c>
+      <c r="T24" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>154</v>
+      </c>
+      <c r="U24" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0335570469798658</v>
+      </c>
+      <c r="V24" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2520325203252032</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D25" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>47</v>
+      </c>
+      <c r="E25" s="3">
+        <v>86</v>
+      </c>
+      <c r="F25">
+        <v>24</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.27906976744186046</v>
+      </c>
+      <c r="N25" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.3255813953488372E-2</v>
+      </c>
+      <c r="O25" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8297872340425532</v>
+      </c>
+      <c r="Q25" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.51063829787234039</v>
+      </c>
+      <c r="R25" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.2553191489361701E-2</v>
+      </c>
+      <c r="S25" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T25" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>140</v>
+      </c>
+      <c r="U25" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.978723404255319</v>
+      </c>
+      <c r="V25" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6279069767441861</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="N8:N1048576 M1:M19">
+  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C25">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E1048576 D1:D25">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F1048576 E1:E25">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:G1048576 F1:F25">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H25">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8:H1048576 G1:G25">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N8:N1048576 M1:M25">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -2096,7 +2640,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O1048576 N1:N19">
+  <conditionalFormatting sqref="O8:O1048576 N1:N25">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -2108,7 +2652,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P8:Q1048576 O1:P19">
+  <conditionalFormatting sqref="P8:Q1048576 O1:P25">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -2120,67 +2664,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F1048576 E1:E19">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G1048576 F1:F19">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H1048576 G1:G19">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C19">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E1048576 D1:D19">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R8:R1048576 Q1:Q19">
+  <conditionalFormatting sqref="R8:R1048576 Q1:Q25">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2192,7 +2676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S8:S1048576 R1:R19">
+  <conditionalFormatting sqref="S8:S1048576 R1:R25">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2204,7 +2688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T1048576 S1:S19">
+  <conditionalFormatting sqref="T8:T1048576 S1:S25">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -2216,7 +2700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U8:U1048576 T1:T19">
+  <conditionalFormatting sqref="U8:U1048576 T1:T25">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2228,7 +2712,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V8:V1048576 U1:U19">
+  <conditionalFormatting sqref="V8:V1048576 U1:U25">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2240,20 +2724,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W1048576 V1:V19">
+  <conditionalFormatting sqref="W8:W1048576 V1:V25">
     <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H19">
-    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/Python/Thingiverse/model_stats.xlsx
+++ b/Python/Thingiverse/model_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Thingiverse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E9C4E2-ABA6-4FBC-85D3-9AA6DE276AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73043A7F-DF0D-46A8-86A9-5CD165CA681F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
   <si>
     <t>Mammoth</t>
   </si>
@@ -208,8 +208,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V25" totalsRowShown="0">
-  <autoFilter ref="A1:V25" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V31" totalsRowShown="0">
+  <autoFilter ref="A1:V31" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
   <tableColumns count="22">
     <tableColumn id="22" xr3:uid="{B838C6CD-92E8-4070-81DB-2EDE900509A2}" name="Date"/>
     <tableColumn id="1" xr3:uid="{C06BFB11-D5FB-45F8-853C-B38F6CA36FF6}" name="Model"/>
@@ -557,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC85C3B-1FD4-46FE-8A2F-07E281673B93}">
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -2555,8 +2555,482 @@
         <v>1.6279069767441861</v>
       </c>
     </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D26" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>302</v>
+      </c>
+      <c r="E26" s="3">
+        <v>697</v>
+      </c>
+      <c r="F26">
+        <v>159</v>
+      </c>
+      <c r="G26">
+        <v>12</v>
+      </c>
+      <c r="H26">
+        <v>5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.22812051649928264</v>
+      </c>
+      <c r="N26" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.721664275466284E-2</v>
+      </c>
+      <c r="O26" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>7.1736011477761836E-3</v>
+      </c>
+      <c r="P26" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3079470198675498</v>
+      </c>
+      <c r="Q26" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.52649006622516559</v>
+      </c>
+      <c r="R26" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.9735099337748346E-2</v>
+      </c>
+      <c r="S26" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6556291390728478E-2</v>
+      </c>
+      <c r="T26" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1071</v>
+      </c>
+      <c r="U26" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5463576158940397</v>
+      </c>
+      <c r="V26" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5365853658536586</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D27" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>301</v>
+      </c>
+      <c r="E27" s="3">
+        <v>337</v>
+      </c>
+      <c r="F27">
+        <v>95</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.28189910979228489</v>
+      </c>
+      <c r="N27" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.483679525222552E-2</v>
+      </c>
+      <c r="O27" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.967359050445104E-3</v>
+      </c>
+      <c r="P27" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1196013289036544</v>
+      </c>
+      <c r="Q27" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.31561461794019935</v>
+      </c>
+      <c r="R27" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6611295681063124E-2</v>
+      </c>
+      <c r="S27" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.3222591362126247E-3</v>
+      </c>
+      <c r="T27" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>546</v>
+      </c>
+      <c r="U27" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8139534883720929</v>
+      </c>
+      <c r="V27" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6201780415430267</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D28" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>156</v>
+      </c>
+      <c r="E28" s="3">
+        <v>236</v>
+      </c>
+      <c r="F28">
+        <v>102</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.43220338983050849</v>
+      </c>
+      <c r="N28" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1186440677966101E-2</v>
+      </c>
+      <c r="O28" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5128205128205128</v>
+      </c>
+      <c r="Q28" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.65384615384615385</v>
+      </c>
+      <c r="R28" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.2051282051282048E-2</v>
+      </c>
+      <c r="S28" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T28" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>455</v>
+      </c>
+      <c r="U28" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9166666666666665</v>
+      </c>
+      <c r="V28" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9279661016949152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D29" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>336</v>
+      </c>
+      <c r="E29" s="3">
+        <v>167</v>
+      </c>
+      <c r="F29">
+        <v>31</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.18562874251497005</v>
+      </c>
+      <c r="N29" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>5.9880239520958087E-3</v>
+      </c>
+      <c r="O29" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.9880239520958087E-3</v>
+      </c>
+      <c r="P29" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.49702380952380953</v>
+      </c>
+      <c r="Q29" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.2261904761904767E-2</v>
+      </c>
+      <c r="R29" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.976190476190476E-3</v>
+      </c>
+      <c r="S29" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.976190476190476E-3</v>
+      </c>
+      <c r="T29" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>236</v>
+      </c>
+      <c r="U29" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.70238095238095233</v>
+      </c>
+      <c r="V29" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4131736526946108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D30" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>154</v>
+      </c>
+      <c r="E30" s="3">
+        <v>125</v>
+      </c>
+      <c r="F30">
+        <v>15</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.12</v>
+      </c>
+      <c r="N30" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="O30" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="P30" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.81168831168831168</v>
+      </c>
+      <c r="Q30" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.7402597402597407E-2</v>
+      </c>
+      <c r="R30" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.4935064935064939E-3</v>
+      </c>
+      <c r="S30" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>6.4935064935064939E-3</v>
+      </c>
+      <c r="T30" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>162</v>
+      </c>
+      <c r="U30" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.051948051948052</v>
+      </c>
+      <c r="V30" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.296</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D31" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>52</v>
+      </c>
+      <c r="E31" s="3">
+        <v>96</v>
+      </c>
+      <c r="F31">
+        <v>27</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.28125</v>
+      </c>
+      <c r="N31" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="O31" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8461538461538463</v>
+      </c>
+      <c r="Q31" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.51923076923076927</v>
+      </c>
+      <c r="R31" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.8461538461538464E-2</v>
+      </c>
+      <c r="S31" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T31" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>156</v>
+      </c>
+      <c r="U31" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3</v>
+      </c>
+      <c r="V31" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.625</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C25">
+  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C31">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -2568,7 +3042,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E1048576 D1:D25">
+  <conditionalFormatting sqref="E8:E1048576 D1:D31">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -2580,7 +3054,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F1048576 E1:E25">
+  <conditionalFormatting sqref="F8:F1048576 E1:E31">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -2592,7 +3066,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G1048576 F1:F25">
+  <conditionalFormatting sqref="G8:G1048576 F1:F31">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -2604,7 +3078,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H25">
+  <conditionalFormatting sqref="H1:H31">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2616,7 +3090,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H1048576 G1:G25">
+  <conditionalFormatting sqref="H8:H1048576 G1:G31">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -2628,7 +3102,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N8:N1048576 M1:M25">
+  <conditionalFormatting sqref="N8:N1048576 M1:M31">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -2640,7 +3114,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O1048576 N1:N25">
+  <conditionalFormatting sqref="O8:O1048576 N1:N31">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -2652,7 +3126,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P8:Q1048576 O1:P25">
+  <conditionalFormatting sqref="P8:Q1048576 O1:P31">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -2664,7 +3138,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R8:R1048576 Q1:Q25">
+  <conditionalFormatting sqref="R8:R1048576 Q1:Q31">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2676,7 +3150,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S8:S1048576 R1:R25">
+  <conditionalFormatting sqref="S8:S1048576 R1:R31">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -2688,7 +3162,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T1048576 S1:S25">
+  <conditionalFormatting sqref="T8:T1048576 S1:S31">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -2700,7 +3174,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U8:U1048576 T1:T25">
+  <conditionalFormatting sqref="U8:U1048576 T1:T31">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2712,7 +3186,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V8:V1048576 U1:U25">
+  <conditionalFormatting sqref="V8:V1048576 U1:U31">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2724,7 +3198,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W1048576 V1:V25">
+  <conditionalFormatting sqref="W8:W1048576 V1:V31">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>

--- a/Python/Thingiverse/model_stats.xlsx
+++ b/Python/Thingiverse/model_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Thingiverse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73043A7F-DF0D-46A8-86A9-5CD165CA681F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D42A60-37D6-444F-AA94-4E207F978E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
   <si>
     <t>Mammoth</t>
   </si>
@@ -208,8 +208,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V31" totalsRowShown="0">
-  <autoFilter ref="A1:V31" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V37" totalsRowShown="0">
+  <autoFilter ref="A1:V37" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
   <tableColumns count="22">
     <tableColumn id="22" xr3:uid="{B838C6CD-92E8-4070-81DB-2EDE900509A2}" name="Date"/>
     <tableColumn id="1" xr3:uid="{C06BFB11-D5FB-45F8-853C-B38F6CA36FF6}" name="Model"/>
@@ -557,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC85C3B-1FD4-46FE-8A2F-07E281673B93}">
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:W37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -3029,8 +3029,482 @@
         <v>1.625</v>
       </c>
     </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D32" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>308</v>
+      </c>
+      <c r="E32" s="3">
+        <v>713</v>
+      </c>
+      <c r="F32">
+        <v>162</v>
+      </c>
+      <c r="G32">
+        <v>12</v>
+      </c>
+      <c r="H32">
+        <v>5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.22720897615708274</v>
+      </c>
+      <c r="N32" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6830294530154277E-2</v>
+      </c>
+      <c r="O32" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>7.0126227208976155E-3</v>
+      </c>
+      <c r="P32" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3149350649350651</v>
+      </c>
+      <c r="Q32" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.52597402597402598</v>
+      </c>
+      <c r="R32" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.896103896103896E-2</v>
+      </c>
+      <c r="S32" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6233766233766232E-2</v>
+      </c>
+      <c r="T32" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1093</v>
+      </c>
+      <c r="U32" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5487012987012987</v>
+      </c>
+      <c r="V32" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5329593267882189</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D33" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>307</v>
+      </c>
+      <c r="E33" s="3">
+        <v>341</v>
+      </c>
+      <c r="F33">
+        <v>96</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.28152492668621704</v>
+      </c>
+      <c r="N33" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.466275659824047E-2</v>
+      </c>
+      <c r="O33" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.9325513196480938E-3</v>
+      </c>
+      <c r="P33" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1107491856677525</v>
+      </c>
+      <c r="Q33" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.31270358306188922</v>
+      </c>
+      <c r="R33" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6286644951140065E-2</v>
+      </c>
+      <c r="S33" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.2573289902280132E-3</v>
+      </c>
+      <c r="T33" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>552</v>
+      </c>
+      <c r="U33" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.7980456026058631</v>
+      </c>
+      <c r="V33" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6187683284457477</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D34" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>162</v>
+      </c>
+      <c r="E34" s="3">
+        <v>242</v>
+      </c>
+      <c r="F34">
+        <v>102</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.42148760330578511</v>
+      </c>
+      <c r="N34" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0661157024793389E-2</v>
+      </c>
+      <c r="O34" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4938271604938271</v>
+      </c>
+      <c r="Q34" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.62962962962962965</v>
+      </c>
+      <c r="R34" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.0864197530864196E-2</v>
+      </c>
+      <c r="S34" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T34" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>461</v>
+      </c>
+      <c r="U34" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.8456790123456792</v>
+      </c>
+      <c r="V34" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9049586776859504</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D35" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>342</v>
+      </c>
+      <c r="E35" s="3">
+        <v>168</v>
+      </c>
+      <c r="F35">
+        <v>31</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.18452380952380953</v>
+      </c>
+      <c r="N35" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7857142857142856E-2</v>
+      </c>
+      <c r="O35" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.1904761904761904E-2</v>
+      </c>
+      <c r="P35" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.49122807017543857</v>
+      </c>
+      <c r="Q35" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.0643274853801165E-2</v>
+      </c>
+      <c r="R35" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>8.771929824561403E-3</v>
+      </c>
+      <c r="S35" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.8479532163742687E-3</v>
+      </c>
+      <c r="T35" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>247</v>
+      </c>
+      <c r="U35" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="V35" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4702380952380953</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D36" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>160</v>
+      </c>
+      <c r="E36" s="3">
+        <v>126</v>
+      </c>
+      <c r="F36">
+        <v>15</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="N36" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>7.9365079365079361E-3</v>
+      </c>
+      <c r="O36" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>7.9365079365079361E-3</v>
+      </c>
+      <c r="P36" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="Q36" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.375E-2</v>
+      </c>
+      <c r="R36" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="S36" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="T36" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>163</v>
+      </c>
+      <c r="U36" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.01875</v>
+      </c>
+      <c r="V36" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2936507936507937</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D37" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>58</v>
+      </c>
+      <c r="E37" s="3">
+        <v>99</v>
+      </c>
+      <c r="F37">
+        <v>27</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="N37" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0202020202020204E-2</v>
+      </c>
+      <c r="O37" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P37" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.7068965517241379</v>
+      </c>
+      <c r="Q37" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.46551724137931033</v>
+      </c>
+      <c r="R37" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="S37" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T37" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>159</v>
+      </c>
+      <c r="U37" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.7413793103448274</v>
+      </c>
+      <c r="V37" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.606060606060606</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C31">
+  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C37">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -3042,7 +3516,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E1048576 D1:D31">
+  <conditionalFormatting sqref="E8:E1048576 D1:D37">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -3054,7 +3528,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F1048576 E1:E31">
+  <conditionalFormatting sqref="F8:F1048576 E1:E37">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -3066,7 +3540,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G1048576 F1:F31">
+  <conditionalFormatting sqref="G8:G1048576 F1:F37">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -3078,7 +3552,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H31">
+  <conditionalFormatting sqref="H1:H37">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -3090,7 +3564,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H1048576 G1:G31">
+  <conditionalFormatting sqref="H8:H1048576 G1:G37">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -3102,7 +3576,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N8:N1048576 M1:M31">
+  <conditionalFormatting sqref="N8:N1048576 M1:M37">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -3114,7 +3588,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O1048576 N1:N31">
+  <conditionalFormatting sqref="O8:O1048576 N1:N37">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -3126,7 +3600,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P8:Q1048576 O1:P31">
+  <conditionalFormatting sqref="P8:Q1048576 O1:P37">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -3138,7 +3612,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R8:R1048576 Q1:Q31">
+  <conditionalFormatting sqref="R8:R1048576 Q1:Q37">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -3150,7 +3624,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S8:S1048576 R1:R31">
+  <conditionalFormatting sqref="S8:S1048576 R1:R37">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -3162,7 +3636,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T1048576 S1:S31">
+  <conditionalFormatting sqref="T8:T1048576 S1:S37">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -3174,7 +3648,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U8:U1048576 T1:T31">
+  <conditionalFormatting sqref="U8:U1048576 T1:T37">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -3186,7 +3660,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V8:V1048576 U1:U31">
+  <conditionalFormatting sqref="V8:V1048576 U1:U37">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -3198,7 +3672,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W1048576 V1:V31">
+  <conditionalFormatting sqref="W8:W1048576 V1:V37">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>

--- a/Python/Thingiverse/model_stats.xlsx
+++ b/Python/Thingiverse/model_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Thingiverse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D42A60-37D6-444F-AA94-4E207F978E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1D7FE8-1FA4-4BA1-BCAC-59B416811F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>Mammoth</t>
   </si>
@@ -208,8 +208,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V37" totalsRowShown="0">
-  <autoFilter ref="A1:V37" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V43" totalsRowShown="0">
+  <autoFilter ref="A1:V43" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
   <tableColumns count="22">
     <tableColumn id="22" xr3:uid="{B838C6CD-92E8-4070-81DB-2EDE900509A2}" name="Date"/>
     <tableColumn id="1" xr3:uid="{C06BFB11-D5FB-45F8-853C-B38F6CA36FF6}" name="Model"/>
@@ -557,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC85C3B-1FD4-46FE-8A2F-07E281673B93}">
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:W43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -3503,8 +3503,482 @@
         <v>1.606060606060606</v>
       </c>
     </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D38" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>315</v>
+      </c>
+      <c r="E38" s="3">
+        <v>733</v>
+      </c>
+      <c r="F38">
+        <v>167</v>
+      </c>
+      <c r="G38">
+        <v>13</v>
+      </c>
+      <c r="H38">
+        <v>5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.22783083219645292</v>
+      </c>
+      <c r="N38" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7735334242837655E-2</v>
+      </c>
+      <c r="O38" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.8212824010914054E-3</v>
+      </c>
+      <c r="P38" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3269841269841272</v>
+      </c>
+      <c r="Q38" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.53015873015873016</v>
+      </c>
+      <c r="R38" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.1269841269841269E-2</v>
+      </c>
+      <c r="S38" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5873015873015872E-2</v>
+      </c>
+      <c r="T38" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1126</v>
+      </c>
+      <c r="U38" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5746031746031748</v>
+      </c>
+      <c r="V38" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5361527967257844</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D39" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>314</v>
+      </c>
+      <c r="E39" s="3">
+        <v>348</v>
+      </c>
+      <c r="F39">
+        <v>103</v>
+      </c>
+      <c r="G39">
+        <v>7</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29597701149425287</v>
+      </c>
+      <c r="N39" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0114942528735632E-2</v>
+      </c>
+      <c r="O39" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.8735632183908046E-3</v>
+      </c>
+      <c r="P39" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.10828025477707</v>
+      </c>
+      <c r="Q39" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.32802547770700635</v>
+      </c>
+      <c r="R39" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2292993630573247E-2</v>
+      </c>
+      <c r="S39" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.1847133757961785E-3</v>
+      </c>
+      <c r="T39" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>579</v>
+      </c>
+      <c r="U39" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8439490445859872</v>
+      </c>
+      <c r="V39" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6637931034482758</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D40" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>169</v>
+      </c>
+      <c r="E40" s="3">
+        <v>246</v>
+      </c>
+      <c r="F40">
+        <v>103</v>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.41869918699186992</v>
+      </c>
+      <c r="N40" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.032520325203252E-2</v>
+      </c>
+      <c r="O40" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P40" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.455621301775148</v>
+      </c>
+      <c r="Q40" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.60946745562130178</v>
+      </c>
+      <c r="R40" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9585798816568046E-2</v>
+      </c>
+      <c r="S40" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T40" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>467</v>
+      </c>
+      <c r="U40" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.7633136094674557</v>
+      </c>
+      <c r="V40" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8983739837398375</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D41" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>349</v>
+      </c>
+      <c r="E41" s="3">
+        <v>172</v>
+      </c>
+      <c r="F41">
+        <v>34</v>
+      </c>
+      <c r="G41">
+        <v>3</v>
+      </c>
+      <c r="H41">
+        <v>2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19767441860465115</v>
+      </c>
+      <c r="N41" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7441860465116279E-2</v>
+      </c>
+      <c r="O41" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.1627906976744186E-2</v>
+      </c>
+      <c r="P41" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.49283667621776506</v>
+      </c>
+      <c r="Q41" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.7421203438395415E-2</v>
+      </c>
+      <c r="R41" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>8.5959885386819486E-3</v>
+      </c>
+      <c r="S41" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.7306590257879654E-3</v>
+      </c>
+      <c r="T41" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>257</v>
+      </c>
+      <c r="U41" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.73638968481375355</v>
+      </c>
+      <c r="V41" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4941860465116279</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D42" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>167</v>
+      </c>
+      <c r="E42" s="3">
+        <v>131</v>
+      </c>
+      <c r="F42">
+        <v>15</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.11450381679389313</v>
+      </c>
+      <c r="N42" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>7.6335877862595417E-3</v>
+      </c>
+      <c r="O42" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>7.6335877862595417E-3</v>
+      </c>
+      <c r="P42" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.78443113772455086</v>
+      </c>
+      <c r="Q42" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.9820359281437126E-2</v>
+      </c>
+      <c r="R42" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>5.9880239520958087E-3</v>
+      </c>
+      <c r="S42" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.9880239520958087E-3</v>
+      </c>
+      <c r="T42" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>168</v>
+      </c>
+      <c r="U42" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0059880239520957</v>
+      </c>
+      <c r="V42" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.282442748091603</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D43" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>65</v>
+      </c>
+      <c r="E43" s="3">
+        <v>101</v>
+      </c>
+      <c r="F43">
+        <v>28</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.27722772277227725</v>
+      </c>
+      <c r="N43" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9801980198019802E-2</v>
+      </c>
+      <c r="O43" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P43" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5538461538461539</v>
+      </c>
+      <c r="Q43" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.43076923076923079</v>
+      </c>
+      <c r="R43" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.0769230769230771E-2</v>
+      </c>
+      <c r="S43" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T43" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>163</v>
+      </c>
+      <c r="U43" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.5076923076923077</v>
+      </c>
+      <c r="V43" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.613861386138614</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C37">
+  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C43">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -3516,7 +3990,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E1048576 D1:D37">
+  <conditionalFormatting sqref="E8:E1048576 D1:D43">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -3528,7 +4002,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F1048576 E1:E37">
+  <conditionalFormatting sqref="F8:F1048576 E1:E43">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -3540,7 +4014,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G1048576 F1:F37">
+  <conditionalFormatting sqref="G8:G1048576 F1:F43">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -3552,7 +4026,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H37">
+  <conditionalFormatting sqref="H1:H43">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -3564,7 +4038,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H1048576 G1:G37">
+  <conditionalFormatting sqref="H8:H1048576 G1:G43">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -3576,7 +4050,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N8:N1048576 M1:M37">
+  <conditionalFormatting sqref="N8:N1048576 M1:M43">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -3588,7 +4062,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O1048576 N1:N37">
+  <conditionalFormatting sqref="O8:O1048576 N1:N43">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -3600,7 +4074,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P8:Q1048576 O1:P37">
+  <conditionalFormatting sqref="P8:Q1048576 O1:P43">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -3612,7 +4086,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R8:R1048576 Q1:Q37">
+  <conditionalFormatting sqref="R8:R1048576 Q1:Q43">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -3624,7 +4098,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S8:S1048576 R1:R37">
+  <conditionalFormatting sqref="S8:S1048576 R1:R43">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -3636,7 +4110,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T1048576 S1:S37">
+  <conditionalFormatting sqref="T8:T1048576 S1:S43">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -3648,7 +4122,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U8:U1048576 T1:T37">
+  <conditionalFormatting sqref="U8:U1048576 T1:T43">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -3660,7 +4134,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V8:V1048576 U1:U37">
+  <conditionalFormatting sqref="V8:V1048576 U1:U43">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -3672,7 +4146,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W1048576 V1:V37">
+  <conditionalFormatting sqref="W8:W1048576 V1:V43">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>

--- a/Python/Thingiverse/model_stats.xlsx
+++ b/Python/Thingiverse/model_stats.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Thingiverse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1D7FE8-1FA4-4BA1-BCAC-59B416811F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9D5CC5-93F2-4C12-AE4C-FCB390671FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="28">
   <si>
     <t>Mammoth</t>
   </si>
@@ -208,8 +208,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V43" totalsRowShown="0">
-  <autoFilter ref="A1:V43" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V73" totalsRowShown="0">
+  <autoFilter ref="A1:V73" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
   <tableColumns count="22">
     <tableColumn id="22" xr3:uid="{B838C6CD-92E8-4070-81DB-2EDE900509A2}" name="Date"/>
     <tableColumn id="1" xr3:uid="{C06BFB11-D5FB-45F8-853C-B38F6CA36FF6}" name="Model"/>
@@ -557,7 +557,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC85C3B-1FD4-46FE-8A2F-07E281673B93}">
-  <dimension ref="A1:W43"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -3977,8 +3978,2378 @@
         <v>1.613861386138614</v>
       </c>
     </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B44" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D44" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>322</v>
+      </c>
+      <c r="E44" s="3">
+        <v>745</v>
+      </c>
+      <c r="F44">
+        <v>173</v>
+      </c>
+      <c r="G44">
+        <v>13</v>
+      </c>
+      <c r="H44">
+        <v>5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.23221476510067113</v>
+      </c>
+      <c r="N44" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.74496644295302E-2</v>
+      </c>
+      <c r="O44" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.7114093959731542E-3</v>
+      </c>
+      <c r="P44" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3136645962732918</v>
+      </c>
+      <c r="Q44" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.53726708074534157</v>
+      </c>
+      <c r="R44" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.0372670807453416E-2</v>
+      </c>
+      <c r="S44" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5527950310559006E-2</v>
+      </c>
+      <c r="T44" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1150</v>
+      </c>
+      <c r="U44" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="V44" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5436241610738255</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D45" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>321</v>
+      </c>
+      <c r="E45" s="3">
+        <v>358</v>
+      </c>
+      <c r="F45">
+        <v>108</v>
+      </c>
+      <c r="G45">
+        <v>7</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.3016759776536313</v>
+      </c>
+      <c r="N45" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9553072625698324E-2</v>
+      </c>
+      <c r="O45" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.7932960893854749E-3</v>
+      </c>
+      <c r="P45" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1152647975077881</v>
+      </c>
+      <c r="Q45" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.3364485981308411</v>
+      </c>
+      <c r="R45" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.1806853582554516E-2</v>
+      </c>
+      <c r="S45" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.1152647975077881E-3</v>
+      </c>
+      <c r="T45" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>599</v>
+      </c>
+      <c r="U45" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8660436137071652</v>
+      </c>
+      <c r="V45" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6731843575418994</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D46" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>176</v>
+      </c>
+      <c r="E46" s="3">
+        <v>255</v>
+      </c>
+      <c r="F46">
+        <v>104</v>
+      </c>
+      <c r="G46">
+        <v>5</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.40784313725490196</v>
+      </c>
+      <c r="N46" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9607843137254902E-2</v>
+      </c>
+      <c r="O46" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P46" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4488636363636365</v>
+      </c>
+      <c r="Q46" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.59090909090909094</v>
+      </c>
+      <c r="R46" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.8409090909090908E-2</v>
+      </c>
+      <c r="S46" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T46" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>478</v>
+      </c>
+      <c r="U46" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.7159090909090908</v>
+      </c>
+      <c r="V46" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8745098039215686</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D47" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>356</v>
+      </c>
+      <c r="E47" s="3">
+        <v>174</v>
+      </c>
+      <c r="F47">
+        <v>34</v>
+      </c>
+      <c r="G47">
+        <v>3</v>
+      </c>
+      <c r="H47">
+        <v>2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19540229885057472</v>
+      </c>
+      <c r="N47" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7241379310344827E-2</v>
+      </c>
+      <c r="O47" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.1494252873563218E-2</v>
+      </c>
+      <c r="P47" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.4887640449438202</v>
+      </c>
+      <c r="Q47" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.5505617977528087E-2</v>
+      </c>
+      <c r="R47" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>8.4269662921348312E-3</v>
+      </c>
+      <c r="S47" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.6179775280898875E-3</v>
+      </c>
+      <c r="T47" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>259</v>
+      </c>
+      <c r="U47" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.72752808988764039</v>
+      </c>
+      <c r="V47" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4885057471264367</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D48" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>174</v>
+      </c>
+      <c r="E48" s="3">
+        <v>134</v>
+      </c>
+      <c r="F48">
+        <v>16</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.11940298507462686</v>
+      </c>
+      <c r="N48" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>7.462686567164179E-3</v>
+      </c>
+      <c r="O48" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>7.462686567164179E-3</v>
+      </c>
+      <c r="P48" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.77011494252873558</v>
+      </c>
+      <c r="Q48" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.1954022988505746E-2</v>
+      </c>
+      <c r="R48" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>5.7471264367816091E-3</v>
+      </c>
+      <c r="S48" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.7471264367816091E-3</v>
+      </c>
+      <c r="T48" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>173</v>
+      </c>
+      <c r="U48" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.99425287356321834</v>
+      </c>
+      <c r="V48" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.291044776119403</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D49" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>72</v>
+      </c>
+      <c r="E49" s="3">
+        <v>105</v>
+      </c>
+      <c r="F49">
+        <v>31</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29523809523809524</v>
+      </c>
+      <c r="N49" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9047619047619049E-2</v>
+      </c>
+      <c r="O49" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P49" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4583333333333333</v>
+      </c>
+      <c r="Q49" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="R49" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="S49" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T49" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>173</v>
+      </c>
+      <c r="U49" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.4027777777777777</v>
+      </c>
+      <c r="V49" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6476190476190475</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B50" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D50" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>329</v>
+      </c>
+      <c r="E50" s="3">
+        <v>750</v>
+      </c>
+      <c r="F50">
+        <v>176</v>
+      </c>
+      <c r="G50">
+        <v>13</v>
+      </c>
+      <c r="H50">
+        <v>5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.23466666666666666</v>
+      </c>
+      <c r="N50" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7333333333333333E-2</v>
+      </c>
+      <c r="O50" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="P50" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2796352583586628</v>
+      </c>
+      <c r="Q50" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.53495440729483279</v>
+      </c>
+      <c r="R50" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.9513677811550151E-2</v>
+      </c>
+      <c r="S50" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5197568389057751E-2</v>
+      </c>
+      <c r="T50" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1161</v>
+      </c>
+      <c r="U50" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5288753799392096</v>
+      </c>
+      <c r="V50" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.548</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D51" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>328</v>
+      </c>
+      <c r="E51" s="3">
+        <v>364</v>
+      </c>
+      <c r="F51">
+        <v>107</v>
+      </c>
+      <c r="G51">
+        <v>8</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29395604395604397</v>
+      </c>
+      <c r="N51" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.197802197802198E-2</v>
+      </c>
+      <c r="O51" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.7472527472527475E-3</v>
+      </c>
+      <c r="P51" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1097560975609757</v>
+      </c>
+      <c r="Q51" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.32621951219512196</v>
+      </c>
+      <c r="R51" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="S51" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.0487804878048782E-3</v>
+      </c>
+      <c r="T51" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>606</v>
+      </c>
+      <c r="U51" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8475609756097562</v>
+      </c>
+      <c r="V51" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6648351648351649</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D52" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>183</v>
+      </c>
+      <c r="E52" s="3">
+        <v>261</v>
+      </c>
+      <c r="F52">
+        <v>106</v>
+      </c>
+      <c r="G52">
+        <v>5</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.4061302681992337</v>
+      </c>
+      <c r="N52" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9157088122605363E-2</v>
+      </c>
+      <c r="O52" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P52" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4262295081967213</v>
+      </c>
+      <c r="Q52" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.57923497267759561</v>
+      </c>
+      <c r="R52" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.7322404371584699E-2</v>
+      </c>
+      <c r="S52" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T52" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>488</v>
+      </c>
+      <c r="U52" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="V52" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8697318007662835</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D53" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>363</v>
+      </c>
+      <c r="E53" s="3">
+        <v>175</v>
+      </c>
+      <c r="F53">
+        <v>34</v>
+      </c>
+      <c r="G53">
+        <v>3</v>
+      </c>
+      <c r="H53">
+        <v>2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19428571428571428</v>
+      </c>
+      <c r="N53" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7142857142857144E-2</v>
+      </c>
+      <c r="O53" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.1428571428571429E-2</v>
+      </c>
+      <c r="P53" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.48209366391184572</v>
+      </c>
+      <c r="Q53" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.366391184573003E-2</v>
+      </c>
+      <c r="R53" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>8.2644628099173556E-3</v>
+      </c>
+      <c r="S53" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.5096418732782371E-3</v>
+      </c>
+      <c r="T53" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>260</v>
+      </c>
+      <c r="U53" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.71625344352617082</v>
+      </c>
+      <c r="V53" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4857142857142858</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D54" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>181</v>
+      </c>
+      <c r="E54" s="3">
+        <v>139</v>
+      </c>
+      <c r="F54">
+        <v>16</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.11510791366906475</v>
+      </c>
+      <c r="N54" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>7.1942446043165471E-3</v>
+      </c>
+      <c r="O54" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>7.1942446043165471E-3</v>
+      </c>
+      <c r="P54" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.76795580110497241</v>
+      </c>
+      <c r="Q54" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.8397790055248615E-2</v>
+      </c>
+      <c r="R54" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>5.5248618784530384E-3</v>
+      </c>
+      <c r="S54" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.5248618784530384E-3</v>
+      </c>
+      <c r="T54" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>178</v>
+      </c>
+      <c r="U54" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.98342541436464093</v>
+      </c>
+      <c r="V54" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2805755395683454</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D55" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>79</v>
+      </c>
+      <c r="E55" s="3">
+        <v>110</v>
+      </c>
+      <c r="F55">
+        <v>33</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.3</v>
+      </c>
+      <c r="N55" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8181818181818181E-2</v>
+      </c>
+      <c r="O55" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P55" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3924050632911393</v>
+      </c>
+      <c r="Q55" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.41772151898734178</v>
+      </c>
+      <c r="R55" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.5316455696202531E-2</v>
+      </c>
+      <c r="S55" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T55" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>182</v>
+      </c>
+      <c r="U55" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3037974683544302</v>
+      </c>
+      <c r="V55" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6545454545454545</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B56" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D56" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>336</v>
+      </c>
+      <c r="E56" s="3">
+        <v>764</v>
+      </c>
+      <c r="F56">
+        <v>181</v>
+      </c>
+      <c r="G56">
+        <v>13</v>
+      </c>
+      <c r="H56">
+        <v>5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.23691099476439789</v>
+      </c>
+      <c r="N56" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7015706806282723E-2</v>
+      </c>
+      <c r="O56" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.5445026178010471E-3</v>
+      </c>
+      <c r="P56" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2738095238095237</v>
+      </c>
+      <c r="Q56" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.53869047619047616</v>
+      </c>
+      <c r="R56" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.8690476190476192E-2</v>
+      </c>
+      <c r="S56" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.488095238095238E-2</v>
+      </c>
+      <c r="T56" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1185</v>
+      </c>
+      <c r="U56" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5267857142857144</v>
+      </c>
+      <c r="V56" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5510471204188481</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D57" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>335</v>
+      </c>
+      <c r="E57" s="3">
+        <v>369</v>
+      </c>
+      <c r="F57">
+        <v>108</v>
+      </c>
+      <c r="G57">
+        <v>8</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29268292682926828</v>
+      </c>
+      <c r="N57" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1680216802168022E-2</v>
+      </c>
+      <c r="O57" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.7100271002710027E-3</v>
+      </c>
+      <c r="P57" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1014925373134328</v>
+      </c>
+      <c r="Q57" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.32238805970149254</v>
+      </c>
+      <c r="R57" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3880597014925373E-2</v>
+      </c>
+      <c r="S57" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9850746268656717E-3</v>
+      </c>
+      <c r="T57" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>613</v>
+      </c>
+      <c r="U57" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8298507462686566</v>
+      </c>
+      <c r="V57" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6612466124661247</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D58" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>190</v>
+      </c>
+      <c r="E58" s="3">
+        <v>263</v>
+      </c>
+      <c r="F58">
+        <v>106</v>
+      </c>
+      <c r="G58">
+        <v>6</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.40304182509505704</v>
+      </c>
+      <c r="N58" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2813688212927757E-2</v>
+      </c>
+      <c r="O58" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P58" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3842105263157896</v>
+      </c>
+      <c r="Q58" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.55789473684210522</v>
+      </c>
+      <c r="R58" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.1578947368421054E-2</v>
+      </c>
+      <c r="S58" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T58" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>493</v>
+      </c>
+      <c r="U58" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.594736842105263</v>
+      </c>
+      <c r="V58" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8745247148288973</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D59" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>370</v>
+      </c>
+      <c r="E59" s="3">
+        <v>177</v>
+      </c>
+      <c r="F59">
+        <v>34</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+      <c r="H59">
+        <v>2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19209039548022599</v>
+      </c>
+      <c r="N59" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6949152542372881E-2</v>
+      </c>
+      <c r="O59" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.1299435028248588E-2</v>
+      </c>
+      <c r="P59" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.47837837837837838</v>
+      </c>
+      <c r="Q59" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.1891891891891897E-2</v>
+      </c>
+      <c r="R59" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>8.1081081081081086E-3</v>
+      </c>
+      <c r="S59" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.4054054054054057E-3</v>
+      </c>
+      <c r="T59" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>262</v>
+      </c>
+      <c r="U59" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.70810810810810809</v>
+      </c>
+      <c r="V59" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4802259887005649</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B60" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D60" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>188</v>
+      </c>
+      <c r="E60" s="3">
+        <v>141</v>
+      </c>
+      <c r="F60">
+        <v>17</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.12056737588652482</v>
+      </c>
+      <c r="N60" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>7.0921985815602835E-3</v>
+      </c>
+      <c r="O60" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>7.0921985815602835E-3</v>
+      </c>
+      <c r="P60" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.75</v>
+      </c>
+      <c r="Q60" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.0425531914893623E-2</v>
+      </c>
+      <c r="R60" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>5.3191489361702126E-3</v>
+      </c>
+      <c r="S60" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.3191489361702126E-3</v>
+      </c>
+      <c r="T60" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>182</v>
+      </c>
+      <c r="U60" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.96808510638297873</v>
+      </c>
+      <c r="V60" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2907801418439717</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D61" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>86</v>
+      </c>
+      <c r="E61" s="3">
+        <v>115</v>
+      </c>
+      <c r="F61">
+        <v>35</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.30434782608695654</v>
+      </c>
+      <c r="N61" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7391304347826087E-2</v>
+      </c>
+      <c r="O61" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P61" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3372093023255813</v>
+      </c>
+      <c r="Q61" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.40697674418604651</v>
+      </c>
+      <c r="R61" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3255813953488372E-2</v>
+      </c>
+      <c r="S61" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T61" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>191</v>
+      </c>
+      <c r="U61" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2209302325581395</v>
+      </c>
+      <c r="V61" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6608695652173913</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C62" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D62" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>343</v>
+      </c>
+      <c r="E62" s="3">
+        <v>782</v>
+      </c>
+      <c r="F62">
+        <v>184</v>
+      </c>
+      <c r="G62">
+        <v>13</v>
+      </c>
+      <c r="H62">
+        <v>5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="N62" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6624040920716114E-2</v>
+      </c>
+      <c r="O62" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.3938618925831201E-3</v>
+      </c>
+      <c r="P62" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2798833819241984</v>
+      </c>
+      <c r="Q62" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.53644314868804666</v>
+      </c>
+      <c r="R62" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.7900874635568516E-2</v>
+      </c>
+      <c r="S62" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4577259475218658E-2</v>
+      </c>
+      <c r="T62" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1209</v>
+      </c>
+      <c r="U62" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5247813411078717</v>
+      </c>
+      <c r="V62" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5460358056265984</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D63" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>342</v>
+      </c>
+      <c r="E63" s="3">
+        <v>379</v>
+      </c>
+      <c r="F63">
+        <v>111</v>
+      </c>
+      <c r="G63">
+        <v>8</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29287598944591031</v>
+      </c>
+      <c r="N63" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1108179419525065E-2</v>
+      </c>
+      <c r="O63" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.6385224274406332E-3</v>
+      </c>
+      <c r="P63" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1081871345029239</v>
+      </c>
+      <c r="Q63" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.32456140350877194</v>
+      </c>
+      <c r="R63" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3391812865497075E-2</v>
+      </c>
+      <c r="S63" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9239766081871343E-3</v>
+      </c>
+      <c r="T63" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>629</v>
+      </c>
+      <c r="U63" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8391812865497077</v>
+      </c>
+      <c r="V63" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6596306068601583</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D64" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>197</v>
+      </c>
+      <c r="E64" s="3">
+        <v>272</v>
+      </c>
+      <c r="F64">
+        <v>108</v>
+      </c>
+      <c r="G64">
+        <v>6</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.39705882352941174</v>
+      </c>
+      <c r="N64" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2058823529411766E-2</v>
+      </c>
+      <c r="O64" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P64" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3807106598984771</v>
+      </c>
+      <c r="Q64" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.54822335025380708</v>
+      </c>
+      <c r="R64" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.0456852791878174E-2</v>
+      </c>
+      <c r="S64" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T64" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>506</v>
+      </c>
+      <c r="U64" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.5685279187817258</v>
+      </c>
+      <c r="V64" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8602941176470589</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D65" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>377</v>
+      </c>
+      <c r="E65" s="3">
+        <v>178</v>
+      </c>
+      <c r="F65">
+        <v>35</v>
+      </c>
+      <c r="G65">
+        <v>3</v>
+      </c>
+      <c r="H65">
+        <v>2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19662921348314608</v>
+      </c>
+      <c r="N65" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6853932584269662E-2</v>
+      </c>
+      <c r="O65" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.1235955056179775E-2</v>
+      </c>
+      <c r="P65" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.47214854111405835</v>
+      </c>
+      <c r="Q65" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.2838196286472149E-2</v>
+      </c>
+      <c r="R65" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.9575596816976128E-3</v>
+      </c>
+      <c r="S65" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.3050397877984082E-3</v>
+      </c>
+      <c r="T65" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>265</v>
+      </c>
+      <c r="U65" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.70291777188328908</v>
+      </c>
+      <c r="V65" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4887640449438202</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B66" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D66" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>195</v>
+      </c>
+      <c r="E66" s="3">
+        <v>158</v>
+      </c>
+      <c r="F66">
+        <v>23</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.14556962025316456</v>
+      </c>
+      <c r="N66" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>6.3291139240506328E-3</v>
+      </c>
+      <c r="O66" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.3291139240506328E-3</v>
+      </c>
+      <c r="P66" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.81025641025641026</v>
+      </c>
+      <c r="Q66" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.11794871794871795</v>
+      </c>
+      <c r="R66" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>5.1282051282051282E-3</v>
+      </c>
+      <c r="S66" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.1282051282051282E-3</v>
+      </c>
+      <c r="T66" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>211</v>
+      </c>
+      <c r="U66" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.082051282051282</v>
+      </c>
+      <c r="V66" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.3354430379746836</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D67" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>93</v>
+      </c>
+      <c r="E67" s="3">
+        <v>122</v>
+      </c>
+      <c r="F67">
+        <v>36</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29508196721311475</v>
+      </c>
+      <c r="N67" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6393442622950821E-2</v>
+      </c>
+      <c r="O67" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P67" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3118279569892473</v>
+      </c>
+      <c r="Q67" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.38709677419354838</v>
+      </c>
+      <c r="R67" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.1505376344086023E-2</v>
+      </c>
+      <c r="S67" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T67" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>200</v>
+      </c>
+      <c r="U67" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.150537634408602</v>
+      </c>
+      <c r="V67" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.639344262295082</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B68" t="s">
+        <v>0</v>
+      </c>
+      <c r="C68" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D68" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>350</v>
+      </c>
+      <c r="E68" s="3">
+        <v>799</v>
+      </c>
+      <c r="F68">
+        <v>189</v>
+      </c>
+      <c r="G68">
+        <v>13</v>
+      </c>
+      <c r="H68">
+        <v>5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.23654568210262827</v>
+      </c>
+      <c r="N68" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6270337922403004E-2</v>
+      </c>
+      <c r="O68" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.2578222778473091E-3</v>
+      </c>
+      <c r="P68" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2828571428571429</v>
+      </c>
+      <c r="Q68" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.54</v>
+      </c>
+      <c r="R68" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.7142857142857144E-2</v>
+      </c>
+      <c r="S68" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4285714285714285E-2</v>
+      </c>
+      <c r="T68" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1236</v>
+      </c>
+      <c r="U68" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5314285714285716</v>
+      </c>
+      <c r="V68" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5469336670838547</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D69" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>349</v>
+      </c>
+      <c r="E69" s="3">
+        <v>388</v>
+      </c>
+      <c r="F69">
+        <v>111</v>
+      </c>
+      <c r="G69">
+        <v>8</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.28608247422680411</v>
+      </c>
+      <c r="N69" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0618556701030927E-2</v>
+      </c>
+      <c r="O69" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.5773195876288659E-3</v>
+      </c>
+      <c r="P69" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1117478510028653</v>
+      </c>
+      <c r="Q69" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.31805157593123207</v>
+      </c>
+      <c r="R69" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2922636103151862E-2</v>
+      </c>
+      <c r="S69" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.8653295128939827E-3</v>
+      </c>
+      <c r="T69" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>638</v>
+      </c>
+      <c r="U69" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8280802292263609</v>
+      </c>
+      <c r="V69" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6443298969072164</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2</v>
+      </c>
+      <c r="C70" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D70" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>204</v>
+      </c>
+      <c r="E70" s="3">
+        <v>278</v>
+      </c>
+      <c r="F70">
+        <v>110</v>
+      </c>
+      <c r="G70">
+        <v>6</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.39568345323741005</v>
+      </c>
+      <c r="N70" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1582733812949641E-2</v>
+      </c>
+      <c r="O70" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P70" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3627450980392157</v>
+      </c>
+      <c r="Q70" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.53921568627450978</v>
+      </c>
+      <c r="R70" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.9411764705882353E-2</v>
+      </c>
+      <c r="S70" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T70" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>516</v>
+      </c>
+      <c r="U70" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.5294117647058822</v>
+      </c>
+      <c r="V70" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8561151079136691</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B71" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D71" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>384</v>
+      </c>
+      <c r="E71" s="3">
+        <v>181</v>
+      </c>
+      <c r="F71">
+        <v>37</v>
+      </c>
+      <c r="G71">
+        <v>3</v>
+      </c>
+      <c r="H71">
+        <v>2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.20441988950276244</v>
+      </c>
+      <c r="N71" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6574585635359115E-2</v>
+      </c>
+      <c r="O71" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.1049723756906077E-2</v>
+      </c>
+      <c r="P71" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.47135416666666669</v>
+      </c>
+      <c r="Q71" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.6354166666666671E-2</v>
+      </c>
+      <c r="R71" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.8125E-3</v>
+      </c>
+      <c r="S71" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.208333333333333E-3</v>
+      </c>
+      <c r="T71" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>272</v>
+      </c>
+      <c r="U71" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="V71" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5027624309392265</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B72" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D72" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>202</v>
+      </c>
+      <c r="E72" s="3">
+        <v>161</v>
+      </c>
+      <c r="F72">
+        <v>23</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="N72" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>6.2111801242236021E-3</v>
+      </c>
+      <c r="O72" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.2111801242236021E-3</v>
+      </c>
+      <c r="P72" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.79702970297029707</v>
+      </c>
+      <c r="Q72" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.11386138613861387</v>
+      </c>
+      <c r="R72" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.9504950495049506E-3</v>
+      </c>
+      <c r="S72" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.9504950495049506E-3</v>
+      </c>
+      <c r="T72" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>214</v>
+      </c>
+      <c r="U72" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0594059405940595</v>
+      </c>
+      <c r="V72" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.329192546583851</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D73" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>100</v>
+      </c>
+      <c r="E73" s="3">
+        <v>126</v>
+      </c>
+      <c r="F73">
+        <v>61</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.48412698412698413</v>
+      </c>
+      <c r="N73" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5873015873015872E-2</v>
+      </c>
+      <c r="O73" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P73" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.26</v>
+      </c>
+      <c r="Q73" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.61</v>
+      </c>
+      <c r="R73" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>0.02</v>
+      </c>
+      <c r="S73" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T73" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>254</v>
+      </c>
+      <c r="U73" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.54</v>
+      </c>
+      <c r="V73" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0158730158730158</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C43">
+  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C73">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -3990,7 +6361,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E1048576 D1:D43">
+  <conditionalFormatting sqref="E8:E1048576 D1:D73">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -4002,7 +6373,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F1048576 E1:E43">
+  <conditionalFormatting sqref="F8:F1048576 E1:E73">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -4014,7 +6385,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G1048576 F1:F43">
+  <conditionalFormatting sqref="G8:G1048576 F1:F73">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -4026,7 +6397,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H43">
+  <conditionalFormatting sqref="H1:H73">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -4038,7 +6409,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H1048576 G1:G43">
+  <conditionalFormatting sqref="H8:H1048576 G1:G73">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -4050,7 +6421,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N8:N1048576 M1:M43">
+  <conditionalFormatting sqref="N8:N1048576 M1:M73">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -4062,7 +6433,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O1048576 N1:N43">
+  <conditionalFormatting sqref="O8:O1048576 N1:N73">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -4074,7 +6445,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P8:Q1048576 O1:P43">
+  <conditionalFormatting sqref="P8:Q1048576 O1:P73">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -4086,7 +6457,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R8:R1048576 Q1:Q43">
+  <conditionalFormatting sqref="R8:R1048576 Q1:Q73">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -4098,7 +6469,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S8:S1048576 R1:R43">
+  <conditionalFormatting sqref="S8:S1048576 R1:R73">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -4110,7 +6481,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T1048576 S1:S43">
+  <conditionalFormatting sqref="T8:T1048576 S1:S73">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -4122,7 +6493,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U8:U1048576 T1:T43">
+  <conditionalFormatting sqref="U8:U1048576 T1:T73">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -4134,7 +6505,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V8:V1048576 U1:U43">
+  <conditionalFormatting sqref="V8:V1048576 U1:U73">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -4146,7 +6517,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W1048576 V1:V43">
+  <conditionalFormatting sqref="W8:W1048576 V1:V73">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>

--- a/Python/Thingiverse/model_stats.xlsx
+++ b/Python/Thingiverse/model_stats.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Thingiverse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9D5CC5-93F2-4C12-AE4C-FCB390671FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923F3EBE-0887-4658-9D72-DC860D8DDAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Overall" sheetId="1" r:id="rId1"/>
+    <sheet name="Inventory" sheetId="2" r:id="rId2"/>
+    <sheet name="SubModels" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="131">
   <si>
     <t>Mammoth</t>
   </si>
@@ -110,6 +112,315 @@
   <si>
     <t>Model</t>
   </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Dir</t>
+  </si>
+  <si>
+    <t>ModelName</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\NHL Logos\My Versions\Utah Mammoth</t>
+  </si>
+  <si>
+    <t>Utah_Mammoth</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\PWHL Logos\Boston Fleet</t>
+  </si>
+  <si>
+    <t>Boston_Fleet</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\PWHL Logos\League</t>
+  </si>
+  <si>
+    <t>PWHL_Logo</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\PWHL Logos\Minnesota Frost</t>
+  </si>
+  <si>
+    <t>Minnesota_Frost</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\PWHL Logos\Montreal Victoire</t>
+  </si>
+  <si>
+    <t>montreal_victoire</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\PWHL Logos\New York Sirens</t>
+  </si>
+  <si>
+    <t>New_York_Sirens</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\PWHL Logos\Ottawa Charge</t>
+  </si>
+  <si>
+    <t>Ottawa_Charge</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\PWHL Logos\Seattle Torrent</t>
+  </si>
+  <si>
+    <t>Seattle_Torrent</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\PWHL Logos\Toronto Sceptres</t>
+  </si>
+  <si>
+    <t>Toronto_Sceptres</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\PWHL Logos\Vancouver Goldeneyes</t>
+  </si>
+  <si>
+    <t>Vancouver_Goldeneyes</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Atlanta Dream</t>
+  </si>
+  <si>
+    <t>Atlanta_Dream</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Chicago Sky</t>
+  </si>
+  <si>
+    <t>Chicago_Sky</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Connecticut Sun</t>
+  </si>
+  <si>
+    <t>Connecticut_Sun</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Dallas Wings</t>
+  </si>
+  <si>
+    <t>Dallas_Wings</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Golden State Valkyries</t>
+  </si>
+  <si>
+    <t>Golden_State_Valkyries</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Indiana Fever</t>
+  </si>
+  <si>
+    <t>Indiana_Fever</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Las Vegas Aces</t>
+  </si>
+  <si>
+    <t>Las_Vegas_Aces</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\League Logo</t>
+  </si>
+  <si>
+    <t>WNBA_Logo</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Los Angeles Sparks</t>
+  </si>
+  <si>
+    <t>Los_Angeles_Sparks</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Minnesota Lynx</t>
+  </si>
+  <si>
+    <t>Minnesota_Lynx</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\New York Liberty</t>
+  </si>
+  <si>
+    <t>New_York_Liberty</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Phoenix Mercury</t>
+  </si>
+  <si>
+    <t>Phoenix_Mercury</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Seattle Storm</t>
+  </si>
+  <si>
+    <t>Seattle_Storm</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Toronto Tempo</t>
+  </si>
+  <si>
+    <t>Toronto_Tempo</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\WNBA Logos\Washington Mystics</t>
+  </si>
+  <si>
+    <t>Washington_Mystics</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\NHL Logos\My Versions\Utah Hockey Club</t>
+  </si>
+  <si>
+    <t>Utah_Hockey_Club_Logo</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\Poker Chip Tray\My Version 202505040113</t>
+  </si>
+  <si>
+    <t>Poker_Chip_Tray_Table_Insert</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Baie-Comeau Drakkar</t>
+  </si>
+  <si>
+    <t>Baie-Comeau_Drakkar</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Blainville-Broisbriand Armada</t>
+  </si>
+  <si>
+    <t>Blainville-Broisbriand_Armada</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Cape Breton Screaming Eagles</t>
+  </si>
+  <si>
+    <t>Cape_Breton_Screaming_Eagles</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Charlottetown Islanders</t>
+  </si>
+  <si>
+    <t>Charlottetown_Islanders</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Chicoutimi Sagueneens</t>
+  </si>
+  <si>
+    <t>Chicoutimi_Sageuneens</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Drummondville Voltigeurs</t>
+  </si>
+  <si>
+    <t>Drummondville_Voltigeurs</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Gatineau Olympiques</t>
+  </si>
+  <si>
+    <t>Gatineau_Olympiques</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Halifax Mooseheads</t>
+  </si>
+  <si>
+    <t>Halifax_Mooseheads</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Moncton Wildcats</t>
+  </si>
+  <si>
+    <t>Moncton_Wildcats</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Newfoundland Regiment</t>
+  </si>
+  <si>
+    <t>Newfoundland_Regiment</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Quebec Remparts</t>
+  </si>
+  <si>
+    <t>Quebec_Remparts</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Rimouski Oceanic</t>
+  </si>
+  <si>
+    <t>Rimouski_Oceanic</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Rouyn-Noranda Huskies</t>
+  </si>
+  <si>
+    <t>Rouyn-Noranda_Huskies</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Saint John SeaDogs</t>
+  </si>
+  <si>
+    <t>Saint_John_Seadogs</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Shawinigan Cataractes</t>
+  </si>
+  <si>
+    <t>Shawinigan__Cataractes</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Sherbrooke Phoenix</t>
+  </si>
+  <si>
+    <t>Sherbrooke_Phoenix</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Val Dor Foreurs</t>
+  </si>
+  <si>
+    <t>Val_Dor_Foreurs</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\Victoriaville Tigres</t>
+  </si>
+  <si>
+    <t>Victoriaville_Tigres</t>
+  </si>
+  <si>
+    <t>D:\3D Prints\QMJHL Logos\League Logo</t>
+  </si>
+  <si>
+    <t>QMJHL_League_Logo</t>
+  </si>
+  <si>
+    <t>Thingiverse</t>
+  </si>
+  <si>
+    <t>https://www.thingiverse.com/thing:7160565</t>
+  </si>
+  <si>
+    <t>https://www.thingiverse.com/thing:6999906</t>
+  </si>
+  <si>
+    <t>https://www.thingiverse.com/thing:7031788</t>
+  </si>
+  <si>
+    <t>https://www.thingiverse.com/thing:7031806</t>
+  </si>
+  <si>
+    <t>https://www.thingiverse.com/thing:7054629</t>
+  </si>
+  <si>
+    <t>ThingiverseID</t>
+  </si>
+  <si>
+    <t>https://www.thingiverse.com/thing:7267989</t>
+  </si>
 </sst>
 </file>
 
@@ -157,7 +468,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
@@ -208,16 +522,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V73" totalsRowShown="0">
-  <autoFilter ref="A1:V73" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V115" totalsRowShown="0">
+  <autoFilter ref="A1:V115" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
   <tableColumns count="22">
     <tableColumn id="22" xr3:uid="{B838C6CD-92E8-4070-81DB-2EDE900509A2}" name="Date"/>
     <tableColumn id="1" xr3:uid="{C06BFB11-D5FB-45F8-853C-B38F6CA36FF6}" name="Model"/>
     <tableColumn id="13" xr3:uid="{AEE26F58-911F-4534-94C6-8FCA31D6F4B1}" name="Published"/>
-    <tableColumn id="14" xr3:uid="{11FE9DF7-F747-41F2-BE31-8FAB66C0B838}" name="Age" dataDxfId="11">
+    <tableColumn id="14" xr3:uid="{11FE9DF7-F747-41F2-BE31-8FAB66C0B838}" name="Age" dataDxfId="12">
       <calculatedColumnFormula>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7E393A08-4718-4CB8-8F50-8ACBD51A470F}" name="Views" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{7E393A08-4718-4CB8-8F50-8ACBD51A470F}" name="Views" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{AE7E7C79-96E4-4AA4-8ABE-36217F4A6424}" name="Downloads"/>
     <tableColumn id="4" xr3:uid="{CE18BE4D-786A-4C74-B355-10DEBE9AE05E}" name="Likes"/>
     <tableColumn id="5" xr3:uid="{FDBA26F1-3698-43DB-942B-1D299A4F5F85}" name="Collects"/>
@@ -225,36 +539,64 @@
     <tableColumn id="7" xr3:uid="{6B33EC49-4483-47AF-BF77-28C0945F956C}" name="Comments"/>
     <tableColumn id="8" xr3:uid="{8A03F31E-D992-4A6A-8C83-45976E1E911E}" name="Makes"/>
     <tableColumn id="9" xr3:uid="{50A57524-FA39-4415-AA51-E48AAD714DFB}" name="Derivatives"/>
-    <tableColumn id="10" xr3:uid="{2B3F8FB8-3A77-4903-8157-DF2E632AC885}" name="Pdownload" dataDxfId="9">
+    <tableColumn id="10" xr3:uid="{2B3F8FB8-3A77-4903-8157-DF2E632AC885}" name="Pdownload" dataDxfId="10">
       <calculatedColumnFormula>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4367DED9-9F80-416A-89E4-4D8ABEF630FC}" name="Plike" dataDxfId="8">
+    <tableColumn id="11" xr3:uid="{4367DED9-9F80-416A-89E4-4D8ABEF630FC}" name="Plike" dataDxfId="9">
       <calculatedColumnFormula>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5A4C3180-1515-416E-8B42-B799EDBB03F7}" name="Pcollect" dataDxfId="7">
+    <tableColumn id="12" xr3:uid="{5A4C3180-1515-416E-8B42-B799EDBB03F7}" name="Pcollect" dataDxfId="8">
       <calculatedColumnFormula>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{2ABE97EB-B9BA-49CE-9BEA-121DABE86BAB}" name="DailyViews" dataDxfId="6">
+    <tableColumn id="18" xr3:uid="{2ABE97EB-B9BA-49CE-9BEA-121DABE86BAB}" name="DailyViews" dataDxfId="7">
       <calculatedColumnFormula>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{BE1FE1BE-2BA3-494C-BDA2-F0B3AA590326}" name="DailyDownloads" dataDxfId="5">
+    <tableColumn id="15" xr3:uid="{BE1FE1BE-2BA3-494C-BDA2-F0B3AA590326}" name="DailyDownloads" dataDxfId="6">
       <calculatedColumnFormula>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{630D5AC9-22FD-4648-B35B-8100FA5478DD}" name="DailyLikes" dataDxfId="4">
+    <tableColumn id="16" xr3:uid="{630D5AC9-22FD-4648-B35B-8100FA5478DD}" name="DailyLikes" dataDxfId="5">
       <calculatedColumnFormula>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{7ED5648F-452B-4C2F-A6CC-579131C7D328}" name="DailyCollects" dataDxfId="3">
+    <tableColumn id="17" xr3:uid="{7ED5648F-452B-4C2F-A6CC-579131C7D328}" name="DailyCollects" dataDxfId="4">
       <calculatedColumnFormula>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{7038F531-83DC-4B5A-A836-DAB608EB634A}" name="Score" dataDxfId="2">
+    <tableColumn id="19" xr3:uid="{7038F531-83DC-4B5A-A836-DAB608EB634A}" name="Score" dataDxfId="3">
       <calculatedColumnFormula>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{C98D09FC-8BDA-4AC8-89C9-828522310B20}" name="DailyScore" dataDxfId="1">
+    <tableColumn id="20" xr3:uid="{C98D09FC-8BDA-4AC8-89C9-828522310B20}" name="DailyScore" dataDxfId="2">
       <calculatedColumnFormula>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{7EF6F635-AAC4-4060-A16A-A1E4AE39403B}" name="ScorePerView" dataDxfId="0">
+    <tableColumn id="21" xr3:uid="{7EF6F635-AAC4-4060-A16A-A1E4AE39403B}" name="ScorePerView" dataDxfId="1">
       <calculatedColumnFormula>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{656A8B71-C0C6-440B-BAAB-C9CBE1B90372}" name="Table3" displayName="Table3" ref="A1:F47" totalsRowShown="0">
+  <autoFilter ref="A1:F47" xr:uid="{656A8B71-C0C6-440B-BAAB-C9CBE1B90372}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{C6369277-9E1F-4C5C-9362-569791D1FBFA}" name="Published"/>
+    <tableColumn id="2" xr3:uid="{F74ACAEC-100D-489D-B262-7FA676A0C4AC}" name="Parent"/>
+    <tableColumn id="3" xr3:uid="{296BB50B-21E0-457C-A466-36C9C8E3E741}" name="Dir"/>
+    <tableColumn id="4" xr3:uid="{2429C066-2BDE-4CA0-A0A6-8F1384EF59A5}" name="ModelName"/>
+    <tableColumn id="6" xr3:uid="{387793EC-51F9-4A62-B79A-9011327205DF}" name="ThingiverseID"/>
+    <tableColumn id="5" xr3:uid="{965ED0CA-2C28-4364-A467-A4F5571ADBD1}" name="Thingiverse"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BB676C2C-B3FE-42B4-A6C0-059962FBB89A}" name="Table2" displayName="Table2" ref="A1:D231" totalsRowShown="0">
+  <autoFilter ref="A1:D231" xr:uid="{BB676C2C-B3FE-42B4-A6C0-059962FBB89A}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{E9D80D2D-BB1D-4FDE-90CE-06D854D914ED}" name="Date" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{84AE994F-16AA-4683-9C1D-6B8C3F098F6A}" name="Parent"/>
+    <tableColumn id="3" xr3:uid="{EF41C20E-3CFD-4FB8-9631-3EDA31FC4FA9}" name="ModelName"/>
+    <tableColumn id="4" xr3:uid="{B0E1CD9A-CFB1-441C-97EF-3878C65CA5B8}" name="Downloads"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -558,7 +900,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC85C3B-1FD4-46FE-8A2F-07E281673B93}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:W115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -6348,8 +6690,3420 @@
         <v>2.0158730158730158</v>
       </c>
     </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D74" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>357</v>
+      </c>
+      <c r="E74" s="3">
+        <v>819</v>
+      </c>
+      <c r="F74">
+        <v>198</v>
+      </c>
+      <c r="G74">
+        <v>13</v>
+      </c>
+      <c r="H74">
+        <v>5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.24175824175824176</v>
+      </c>
+      <c r="N74" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5873015873015872E-2</v>
+      </c>
+      <c r="O74" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.105006105006105E-3</v>
+      </c>
+      <c r="P74" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2941176470588234</v>
+      </c>
+      <c r="Q74" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.55462184873949583</v>
+      </c>
+      <c r="R74" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.6414565826330535E-2</v>
+      </c>
+      <c r="S74" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4005602240896359E-2</v>
+      </c>
+      <c r="T74" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1274</v>
+      </c>
+      <c r="U74" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5686274509803924</v>
+      </c>
+      <c r="V74" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5555555555555556</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D75" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>356</v>
+      </c>
+      <c r="E75" s="3">
+        <v>392</v>
+      </c>
+      <c r="F75">
+        <v>111</v>
+      </c>
+      <c r="G75">
+        <v>8</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.28316326530612246</v>
+      </c>
+      <c r="N75" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0408163265306121E-2</v>
+      </c>
+      <c r="O75" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.5510204081632651E-3</v>
+      </c>
+      <c r="P75" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.101123595505618</v>
+      </c>
+      <c r="Q75" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.31179775280898875</v>
+      </c>
+      <c r="R75" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.247191011235955E-2</v>
+      </c>
+      <c r="S75" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.8089887640449437E-3</v>
+      </c>
+      <c r="T75" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>642</v>
+      </c>
+      <c r="U75" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.803370786516854</v>
+      </c>
+      <c r="V75" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6377551020408163</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D76" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>211</v>
+      </c>
+      <c r="E76" s="3">
+        <v>307</v>
+      </c>
+      <c r="F76">
+        <v>184</v>
+      </c>
+      <c r="G76">
+        <v>7</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.59934853420195444</v>
+      </c>
+      <c r="N76" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2801302931596091E-2</v>
+      </c>
+      <c r="O76" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P76" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4549763033175356</v>
+      </c>
+      <c r="Q76" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.87203791469194314</v>
+      </c>
+      <c r="R76" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.3175355450236969E-2</v>
+      </c>
+      <c r="S76" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T76" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>696</v>
+      </c>
+      <c r="U76" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.2985781990521326</v>
+      </c>
+      <c r="V76" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2671009771986972</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B77" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D77" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>391</v>
+      </c>
+      <c r="E77" s="3">
+        <v>184</v>
+      </c>
+      <c r="F77">
+        <v>37</v>
+      </c>
+      <c r="G77">
+        <v>3</v>
+      </c>
+      <c r="H77">
+        <v>2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.20108695652173914</v>
+      </c>
+      <c r="N77" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6304347826086956E-2</v>
+      </c>
+      <c r="O77" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.0869565217391304E-2</v>
+      </c>
+      <c r="P77" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="Q77" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.4629156010230184E-2</v>
+      </c>
+      <c r="R77" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.6726342710997444E-3</v>
+      </c>
+      <c r="S77" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.1150895140664966E-3</v>
+      </c>
+      <c r="T77" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>275</v>
+      </c>
+      <c r="U77" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.70332480818414322</v>
+      </c>
+      <c r="V77" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4945652173913044</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B78" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D78" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>209</v>
+      </c>
+      <c r="E78" s="3">
+        <v>163</v>
+      </c>
+      <c r="F78">
+        <v>23</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.1411042944785276</v>
+      </c>
+      <c r="N78" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>6.1349693251533744E-3</v>
+      </c>
+      <c r="O78" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.1349693251533744E-3</v>
+      </c>
+      <c r="P78" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.77990430622009566</v>
+      </c>
+      <c r="Q78" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.11004784688995216</v>
+      </c>
+      <c r="R78" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.7846889952153108E-3</v>
+      </c>
+      <c r="S78" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.7846889952153108E-3</v>
+      </c>
+      <c r="T78" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>216</v>
+      </c>
+      <c r="U78" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0334928229665072</v>
+      </c>
+      <c r="V78" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.3251533742331287</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D79" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>107</v>
+      </c>
+      <c r="E79" s="3">
+        <v>129</v>
+      </c>
+      <c r="F79">
+        <v>63</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.48837209302325579</v>
+      </c>
+      <c r="N79" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5503875968992248E-2</v>
+      </c>
+      <c r="O79" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P79" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.205607476635514</v>
+      </c>
+      <c r="Q79" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.58878504672897192</v>
+      </c>
+      <c r="R79" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8691588785046728E-2</v>
+      </c>
+      <c r="S79" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T79" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>261</v>
+      </c>
+      <c r="U79" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.4392523364485981</v>
+      </c>
+      <c r="V79" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0232558139534884</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B80" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D80" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>364</v>
+      </c>
+      <c r="E80" s="3">
+        <v>839</v>
+      </c>
+      <c r="F80">
+        <v>206</v>
+      </c>
+      <c r="G80">
+        <v>13</v>
+      </c>
+      <c r="H80">
+        <v>5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.24553039332538737</v>
+      </c>
+      <c r="N80" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5494636471990465E-2</v>
+      </c>
+      <c r="O80" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.9594755661501785E-3</v>
+      </c>
+      <c r="P80" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3049450549450547</v>
+      </c>
+      <c r="Q80" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.56593406593406592</v>
+      </c>
+      <c r="R80" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="S80" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3736263736263736E-2</v>
+      </c>
+      <c r="T80" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1310</v>
+      </c>
+      <c r="U80" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.598901098901099</v>
+      </c>
+      <c r="V80" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5613825983313467</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D81" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>363</v>
+      </c>
+      <c r="E81" s="3">
+        <v>403</v>
+      </c>
+      <c r="F81">
+        <v>124</v>
+      </c>
+      <c r="G81">
+        <v>8</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="N81" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9851116625310174E-2</v>
+      </c>
+      <c r="O81" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.4813895781637717E-3</v>
+      </c>
+      <c r="P81" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1101928374655647</v>
+      </c>
+      <c r="Q81" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.3415977961432507</v>
+      </c>
+      <c r="R81" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2038567493112948E-2</v>
+      </c>
+      <c r="S81" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.7548209366391185E-3</v>
+      </c>
+      <c r="T81" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>679</v>
+      </c>
+      <c r="U81" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8705234159779613</v>
+      </c>
+      <c r="V81" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.684863523573201</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B82" t="s">
+        <v>2</v>
+      </c>
+      <c r="C82" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D82" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>218</v>
+      </c>
+      <c r="E82" s="3">
+        <v>327</v>
+      </c>
+      <c r="F82">
+        <v>200</v>
+      </c>
+      <c r="G82">
+        <v>8</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.6116207951070336</v>
+      </c>
+      <c r="N82" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.4464831804281346E-2</v>
+      </c>
+      <c r="O82" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P82" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5</v>
+      </c>
+      <c r="Q82" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.91743119266055051</v>
+      </c>
+      <c r="R82" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.669724770642202E-2</v>
+      </c>
+      <c r="S82" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T82" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>751</v>
+      </c>
+      <c r="U82" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.4449541284403669</v>
+      </c>
+      <c r="V82" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2966360856269112</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D83" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>398</v>
+      </c>
+      <c r="E83" s="3">
+        <v>190</v>
+      </c>
+      <c r="F83">
+        <v>39</v>
+      </c>
+      <c r="G83">
+        <v>3</v>
+      </c>
+      <c r="H83">
+        <v>2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.20526315789473684</v>
+      </c>
+      <c r="N83" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5789473684210527E-2</v>
+      </c>
+      <c r="O83" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.0526315789473684E-2</v>
+      </c>
+      <c r="P83" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.47738693467336685</v>
+      </c>
+      <c r="Q83" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.7989949748743713E-2</v>
+      </c>
+      <c r="R83" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.537688442211055E-3</v>
+      </c>
+      <c r="S83" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>5.0251256281407036E-3</v>
+      </c>
+      <c r="T83" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>285</v>
+      </c>
+      <c r="U83" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.7160804020100503</v>
+      </c>
+      <c r="V83" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B84" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D84" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>216</v>
+      </c>
+      <c r="E84" s="3">
+        <v>166</v>
+      </c>
+      <c r="F84">
+        <v>23</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.13855421686746988</v>
+      </c>
+      <c r="N84" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>6.024096385542169E-3</v>
+      </c>
+      <c r="O84" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>6.024096385542169E-3</v>
+      </c>
+      <c r="P84" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.76851851851851849</v>
+      </c>
+      <c r="Q84" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.10648148148148148</v>
+      </c>
+      <c r="R84" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.6296296296296294E-3</v>
+      </c>
+      <c r="S84" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.6296296296296294E-3</v>
+      </c>
+      <c r="T84" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>219</v>
+      </c>
+      <c r="U84" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0138888888888888</v>
+      </c>
+      <c r="V84" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.3192771084337349</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D85" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>114</v>
+      </c>
+      <c r="E85" s="3">
+        <v>130</v>
+      </c>
+      <c r="F85">
+        <v>63</v>
+      </c>
+      <c r="G85">
+        <v>2</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.48461538461538461</v>
+      </c>
+      <c r="N85" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5384615384615385E-2</v>
+      </c>
+      <c r="O85" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P85" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1403508771929824</v>
+      </c>
+      <c r="Q85" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.55263157894736847</v>
+      </c>
+      <c r="R85" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.7543859649122806E-2</v>
+      </c>
+      <c r="S85" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T85" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>262</v>
+      </c>
+      <c r="U85" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2982456140350878</v>
+      </c>
+      <c r="V85" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0153846153846153</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B86" t="s">
+        <v>0</v>
+      </c>
+      <c r="C86" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D86" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>371</v>
+      </c>
+      <c r="E86" s="3">
+        <v>845</v>
+      </c>
+      <c r="F86">
+        <v>207</v>
+      </c>
+      <c r="G86">
+        <v>13</v>
+      </c>
+      <c r="H86">
+        <v>5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.24497041420118343</v>
+      </c>
+      <c r="N86" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5384615384615385E-2</v>
+      </c>
+      <c r="O86" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.9171597633136093E-3</v>
+      </c>
+      <c r="P86" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2776280323450133</v>
+      </c>
+      <c r="Q86" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.55795148247978432</v>
+      </c>
+      <c r="R86" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5040431266846361E-2</v>
+      </c>
+      <c r="S86" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3477088948787063E-2</v>
+      </c>
+      <c r="T86" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1318</v>
+      </c>
+      <c r="U86" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5525606469002695</v>
+      </c>
+      <c r="V86" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5597633136094675</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D87" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>370</v>
+      </c>
+      <c r="E87" s="3">
+        <v>413</v>
+      </c>
+      <c r="F87">
+        <v>126</v>
+      </c>
+      <c r="G87">
+        <v>8</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.30508474576271188</v>
+      </c>
+      <c r="N87" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9370460048426151E-2</v>
+      </c>
+      <c r="O87" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.4213075060532689E-3</v>
+      </c>
+      <c r="P87" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1162162162162161</v>
+      </c>
+      <c r="Q87" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.34054054054054056</v>
+      </c>
+      <c r="R87" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.1621621621621623E-2</v>
+      </c>
+      <c r="S87" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.7027027027027029E-3</v>
+      </c>
+      <c r="T87" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>693</v>
+      </c>
+      <c r="U87" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8729729729729729</v>
+      </c>
+      <c r="V87" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6779661016949152</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B88" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D88" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>225</v>
+      </c>
+      <c r="E88" s="3">
+        <v>336</v>
+      </c>
+      <c r="F88">
+        <v>201</v>
+      </c>
+      <c r="G88">
+        <v>8</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.5982142857142857</v>
+      </c>
+      <c r="N88" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.3809523809523808E-2</v>
+      </c>
+      <c r="O88" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P88" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4933333333333334</v>
+      </c>
+      <c r="Q88" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.89333333333333331</v>
+      </c>
+      <c r="R88" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5555555555555556E-2</v>
+      </c>
+      <c r="S88" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T88" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>762</v>
+      </c>
+      <c r="U88" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.3866666666666667</v>
+      </c>
+      <c r="V88" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2678571428571428</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B89" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D89" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>405</v>
+      </c>
+      <c r="E89" s="3">
+        <v>190</v>
+      </c>
+      <c r="F89">
+        <v>39</v>
+      </c>
+      <c r="G89">
+        <v>3</v>
+      </c>
+      <c r="H89">
+        <v>2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.20526315789473684</v>
+      </c>
+      <c r="N89" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5789473684210527E-2</v>
+      </c>
+      <c r="O89" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.0526315789473684E-2</v>
+      </c>
+      <c r="P89" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.46913580246913578</v>
+      </c>
+      <c r="Q89" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.6296296296296297E-2</v>
+      </c>
+      <c r="R89" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="S89" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.9382716049382715E-3</v>
+      </c>
+      <c r="T89" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>285</v>
+      </c>
+      <c r="U89" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.70370370370370372</v>
+      </c>
+      <c r="V89" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B90" t="s">
+        <v>3</v>
+      </c>
+      <c r="C90" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D90" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>223</v>
+      </c>
+      <c r="E90" s="3">
+        <v>175</v>
+      </c>
+      <c r="F90">
+        <v>25</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="N90" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="O90" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="P90" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.7847533632286996</v>
+      </c>
+      <c r="Q90" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.11210762331838565</v>
+      </c>
+      <c r="R90" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.4843049327354259E-3</v>
+      </c>
+      <c r="S90" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.4843049327354259E-3</v>
+      </c>
+      <c r="T90" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>232</v>
+      </c>
+      <c r="U90" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0403587443946187</v>
+      </c>
+      <c r="V90" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.3257142857142856</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D91" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>121</v>
+      </c>
+      <c r="E91" s="3">
+        <v>135</v>
+      </c>
+      <c r="F91">
+        <v>82</v>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.6074074074074074</v>
+      </c>
+      <c r="N91" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4814814814814815E-2</v>
+      </c>
+      <c r="O91" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P91" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.115702479338843</v>
+      </c>
+      <c r="Q91" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.6776859504132231</v>
+      </c>
+      <c r="R91" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.6528925619834711E-2</v>
+      </c>
+      <c r="S91" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T91" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>305</v>
+      </c>
+      <c r="U91" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.5206611570247932</v>
+      </c>
+      <c r="V91" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2592592592592591</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B92" t="s">
+        <v>0</v>
+      </c>
+      <c r="C92" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D92" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>378</v>
+      </c>
+      <c r="E92" s="3">
+        <v>861</v>
+      </c>
+      <c r="F92">
+        <v>210</v>
+      </c>
+      <c r="G92">
+        <v>13</v>
+      </c>
+      <c r="H92">
+        <v>5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.24390243902439024</v>
+      </c>
+      <c r="N92" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5098722415795587E-2</v>
+      </c>
+      <c r="O92" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.8072009291521487E-3</v>
+      </c>
+      <c r="P92" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2777777777777777</v>
+      </c>
+      <c r="Q92" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="R92" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.439153439153439E-2</v>
+      </c>
+      <c r="S92" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3227513227513227E-2</v>
+      </c>
+      <c r="T92" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1340</v>
+      </c>
+      <c r="U92" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5449735449735451</v>
+      </c>
+      <c r="V92" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5563298490127759</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1</v>
+      </c>
+      <c r="C93" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D93" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>377</v>
+      </c>
+      <c r="E93" s="3">
+        <v>422</v>
+      </c>
+      <c r="F93">
+        <v>127</v>
+      </c>
+      <c r="G93">
+        <v>8</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.3009478672985782</v>
+      </c>
+      <c r="N93" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8957345971563982E-2</v>
+      </c>
+      <c r="O93" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.3696682464454978E-3</v>
+      </c>
+      <c r="P93" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1193633952254642</v>
+      </c>
+      <c r="Q93" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.33687002652519893</v>
+      </c>
+      <c r="R93" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.1220159151193633E-2</v>
+      </c>
+      <c r="S93" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.6525198938992041E-3</v>
+      </c>
+      <c r="T93" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>704</v>
+      </c>
+      <c r="U93" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8673740053050398</v>
+      </c>
+      <c r="V93" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6682464454976302</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B94" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D94" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>232</v>
+      </c>
+      <c r="E94" s="3">
+        <v>349</v>
+      </c>
+      <c r="F94">
+        <v>202</v>
+      </c>
+      <c r="G94">
+        <v>8</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.57879656160458448</v>
+      </c>
+      <c r="N94" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2922636103151862E-2</v>
+      </c>
+      <c r="O94" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P94" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5043103448275863</v>
+      </c>
+      <c r="Q94" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.87068965517241381</v>
+      </c>
+      <c r="R94" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="S94" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T94" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>777</v>
+      </c>
+      <c r="U94" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.3491379310344827</v>
+      </c>
+      <c r="V94" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2263610315186249</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B95" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D95" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>412</v>
+      </c>
+      <c r="E95" s="3">
+        <v>195</v>
+      </c>
+      <c r="F95">
+        <v>39</v>
+      </c>
+      <c r="G95">
+        <v>3</v>
+      </c>
+      <c r="H95">
+        <v>2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.2</v>
+      </c>
+      <c r="N95" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5384615384615385E-2</v>
+      </c>
+      <c r="O95" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.0256410256410256E-2</v>
+      </c>
+      <c r="P95" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.47330097087378642</v>
+      </c>
+      <c r="Q95" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.4660194174757281E-2</v>
+      </c>
+      <c r="R95" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.2815533980582527E-3</v>
+      </c>
+      <c r="S95" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.8543689320388345E-3</v>
+      </c>
+      <c r="T95" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>290</v>
+      </c>
+      <c r="U95" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.70388349514563109</v>
+      </c>
+      <c r="V95" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4871794871794872</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B96" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D96" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>230</v>
+      </c>
+      <c r="E96" s="3">
+        <v>182</v>
+      </c>
+      <c r="F96">
+        <v>25</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.13736263736263737</v>
+      </c>
+      <c r="N96" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>5.4945054945054949E-3</v>
+      </c>
+      <c r="O96" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.4945054945054949E-3</v>
+      </c>
+      <c r="P96" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.79130434782608694</v>
+      </c>
+      <c r="Q96" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.10869565217391304</v>
+      </c>
+      <c r="R96" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.3478260869565218E-3</v>
+      </c>
+      <c r="S96" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.3478260869565218E-3</v>
+      </c>
+      <c r="T96" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>239</v>
+      </c>
+      <c r="U96" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0391304347826087</v>
+      </c>
+      <c r="V96" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.3131868131868132</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D97" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>128</v>
+      </c>
+      <c r="E97" s="3">
+        <v>137</v>
+      </c>
+      <c r="F97">
+        <v>82</v>
+      </c>
+      <c r="G97">
+        <v>2</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.59854014598540151</v>
+      </c>
+      <c r="N97" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4598540145985401E-2</v>
+      </c>
+      <c r="O97" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P97" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0703125</v>
+      </c>
+      <c r="Q97" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.640625</v>
+      </c>
+      <c r="R97" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5625E-2</v>
+      </c>
+      <c r="S97" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T97" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>307</v>
+      </c>
+      <c r="U97" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3984375</v>
+      </c>
+      <c r="V97" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2408759124087592</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B98" t="s">
+        <v>0</v>
+      </c>
+      <c r="C98" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D98" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>385</v>
+      </c>
+      <c r="E98" s="3">
+        <v>871</v>
+      </c>
+      <c r="F98">
+        <v>216</v>
+      </c>
+      <c r="G98">
+        <v>13</v>
+      </c>
+      <c r="H98">
+        <v>5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.24799081515499427</v>
+      </c>
+      <c r="N98" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4925373134328358E-2</v>
+      </c>
+      <c r="O98" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.7405281285878304E-3</v>
+      </c>
+      <c r="P98" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2623376623376625</v>
+      </c>
+      <c r="Q98" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.561038961038961</v>
+      </c>
+      <c r="R98" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.3766233766233764E-2</v>
+      </c>
+      <c r="S98" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.2987012987012988E-2</v>
+      </c>
+      <c r="T98" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1362</v>
+      </c>
+      <c r="U98" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5376623376623377</v>
+      </c>
+      <c r="V98" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.563719862227325</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D99" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>384</v>
+      </c>
+      <c r="E99" s="3">
+        <v>426</v>
+      </c>
+      <c r="F99">
+        <v>127</v>
+      </c>
+      <c r="G99">
+        <v>8</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.2981220657276995</v>
+      </c>
+      <c r="N99" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8779342723004695E-2</v>
+      </c>
+      <c r="O99" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.3474178403755869E-3</v>
+      </c>
+      <c r="P99" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.109375</v>
+      </c>
+      <c r="Q99" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.33072916666666669</v>
+      </c>
+      <c r="R99" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="S99" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.6041666666666665E-3</v>
+      </c>
+      <c r="T99" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>708</v>
+      </c>
+      <c r="U99" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.84375</v>
+      </c>
+      <c r="V99" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6619718309859155</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B100" t="s">
+        <v>2</v>
+      </c>
+      <c r="C100" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D100" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>239</v>
+      </c>
+      <c r="E100" s="3">
+        <v>360</v>
+      </c>
+      <c r="F100">
+        <v>206</v>
+      </c>
+      <c r="G100">
+        <v>8</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.57222222222222219</v>
+      </c>
+      <c r="N100" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="O100" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P100" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.506276150627615</v>
+      </c>
+      <c r="Q100" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.86192468619246865</v>
+      </c>
+      <c r="R100" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.3472803347280332E-2</v>
+      </c>
+      <c r="S100" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T100" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>796</v>
+      </c>
+      <c r="U100" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.3305439330543933</v>
+      </c>
+      <c r="V100" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2111111111111112</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D101" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>419</v>
+      </c>
+      <c r="E101" s="3">
+        <v>197</v>
+      </c>
+      <c r="F101">
+        <v>39</v>
+      </c>
+      <c r="G101">
+        <v>3</v>
+      </c>
+      <c r="H101">
+        <v>2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19796954314720813</v>
+      </c>
+      <c r="N101" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5228426395939087E-2</v>
+      </c>
+      <c r="O101" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.015228426395939E-2</v>
+      </c>
+      <c r="P101" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.4701670644391408</v>
+      </c>
+      <c r="Q101" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.3078758949880672E-2</v>
+      </c>
+      <c r="R101" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.1599045346062056E-3</v>
+      </c>
+      <c r="S101" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.7732696897374704E-3</v>
+      </c>
+      <c r="T101" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>292</v>
+      </c>
+      <c r="U101" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.69689737470167068</v>
+      </c>
+      <c r="V101" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4822335025380711</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D102" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>237</v>
+      </c>
+      <c r="E102" s="3">
+        <v>187</v>
+      </c>
+      <c r="F102">
+        <v>25</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.13368983957219252</v>
+      </c>
+      <c r="N102" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>5.3475935828877002E-3</v>
+      </c>
+      <c r="O102" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.3475935828877002E-3</v>
+      </c>
+      <c r="P102" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.78902953586497893</v>
+      </c>
+      <c r="Q102" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.10548523206751055</v>
+      </c>
+      <c r="R102" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.2194092827004216E-3</v>
+      </c>
+      <c r="S102" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.2194092827004216E-3</v>
+      </c>
+      <c r="T102" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>244</v>
+      </c>
+      <c r="U102" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.029535864978903</v>
+      </c>
+      <c r="V102" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.304812834224599</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D103" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>135</v>
+      </c>
+      <c r="E103" s="3">
+        <v>141</v>
+      </c>
+      <c r="F103">
+        <v>82</v>
+      </c>
+      <c r="G103">
+        <v>2</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.58156028368794321</v>
+      </c>
+      <c r="N103" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4184397163120567E-2</v>
+      </c>
+      <c r="O103" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0444444444444445</v>
+      </c>
+      <c r="Q103" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.6074074074074074</v>
+      </c>
+      <c r="R103" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4814814814814815E-2</v>
+      </c>
+      <c r="S103" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T103" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>311</v>
+      </c>
+      <c r="U103" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.3037037037037038</v>
+      </c>
+      <c r="V103" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2056737588652484</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B104" t="s">
+        <v>0</v>
+      </c>
+      <c r="C104" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D104" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>392</v>
+      </c>
+      <c r="E104" s="3">
+        <v>881</v>
+      </c>
+      <c r="F104">
+        <v>217</v>
+      </c>
+      <c r="G104">
+        <v>13</v>
+      </c>
+      <c r="H104">
+        <v>5</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.24631101021566401</v>
+      </c>
+      <c r="N104" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4755959137343927E-2</v>
+      </c>
+      <c r="O104" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.6753688989784334E-3</v>
+      </c>
+      <c r="P104" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2474489795918369</v>
+      </c>
+      <c r="Q104" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.5535714285714286</v>
+      </c>
+      <c r="R104" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.3163265306122451E-2</v>
+      </c>
+      <c r="S104" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.2755102040816327E-2</v>
+      </c>
+      <c r="T104" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1374</v>
+      </c>
+      <c r="U104" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.5051020408163267</v>
+      </c>
+      <c r="V104" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5595913734392735</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1</v>
+      </c>
+      <c r="C105" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D105" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>391</v>
+      </c>
+      <c r="E105" s="3">
+        <v>432</v>
+      </c>
+      <c r="F105">
+        <v>128</v>
+      </c>
+      <c r="G105">
+        <v>8</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="N105" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8518518518518517E-2</v>
+      </c>
+      <c r="O105" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.3148148148148147E-3</v>
+      </c>
+      <c r="P105" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1048593350383631</v>
+      </c>
+      <c r="Q105" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.32736572890025578</v>
+      </c>
+      <c r="R105" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.0460358056265986E-2</v>
+      </c>
+      <c r="S105" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.5575447570332483E-3</v>
+      </c>
+      <c r="T105" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>716</v>
+      </c>
+      <c r="U105" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8312020460358056</v>
+      </c>
+      <c r="V105" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6574074074074074</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B106" t="s">
+        <v>2</v>
+      </c>
+      <c r="C106" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D106" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>246</v>
+      </c>
+      <c r="E106" s="3">
+        <v>371</v>
+      </c>
+      <c r="F106">
+        <v>207</v>
+      </c>
+      <c r="G106">
+        <v>8</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.55795148247978432</v>
+      </c>
+      <c r="N106" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.15633423180593E-2</v>
+      </c>
+      <c r="O106" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P106" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5081300813008129</v>
+      </c>
+      <c r="Q106" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.84146341463414631</v>
+      </c>
+      <c r="R106" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.2520325203252036E-2</v>
+      </c>
+      <c r="S106" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T106" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>809</v>
+      </c>
+      <c r="U106" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.2886178861788617</v>
+      </c>
+      <c r="V106" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1805929919137466</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B107" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D107" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>426</v>
+      </c>
+      <c r="E107" s="3">
+        <v>199</v>
+      </c>
+      <c r="F107">
+        <v>39</v>
+      </c>
+      <c r="G107">
+        <v>3</v>
+      </c>
+      <c r="H107">
+        <v>2</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19597989949748743</v>
+      </c>
+      <c r="N107" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.507537688442211E-2</v>
+      </c>
+      <c r="O107" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>1.0050251256281407E-2</v>
+      </c>
+      <c r="P107" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.46713615023474181</v>
+      </c>
+      <c r="Q107" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.154929577464789E-2</v>
+      </c>
+      <c r="R107" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>7.0422535211267607E-3</v>
+      </c>
+      <c r="S107" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.6948356807511738E-3</v>
+      </c>
+      <c r="T107" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>294</v>
+      </c>
+      <c r="U107" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.6901408450704225</v>
+      </c>
+      <c r="V107" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4773869346733668</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B108" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D108" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>244</v>
+      </c>
+      <c r="E108" s="3">
+        <v>193</v>
+      </c>
+      <c r="F108">
+        <v>25</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.12953367875647667</v>
+      </c>
+      <c r="N108" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>5.1813471502590676E-3</v>
+      </c>
+      <c r="O108" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.1813471502590676E-3</v>
+      </c>
+      <c r="P108" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.79098360655737709</v>
+      </c>
+      <c r="Q108" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.10245901639344263</v>
+      </c>
+      <c r="R108" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>4.0983606557377051E-3</v>
+      </c>
+      <c r="S108" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.0983606557377051E-3</v>
+      </c>
+      <c r="T108" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>250</v>
+      </c>
+      <c r="U108" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0245901639344261</v>
+      </c>
+      <c r="V108" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2953367875647668</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B109" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D109" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>142</v>
+      </c>
+      <c r="E109" s="3">
+        <v>144</v>
+      </c>
+      <c r="F109">
+        <v>82</v>
+      </c>
+      <c r="G109">
+        <v>2</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="N109" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="O109" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P109" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0140845070422535</v>
+      </c>
+      <c r="Q109" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.57746478873239437</v>
+      </c>
+      <c r="R109" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.4084507042253521E-2</v>
+      </c>
+      <c r="S109" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T109" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>314</v>
+      </c>
+      <c r="U109" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.211267605633803</v>
+      </c>
+      <c r="V109" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1805555555555554</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B110" t="s">
+        <v>0</v>
+      </c>
+      <c r="C110" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D110" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>399</v>
+      </c>
+      <c r="E110" s="3">
+        <v>888</v>
+      </c>
+      <c r="F110">
+        <v>218</v>
+      </c>
+      <c r="G110">
+        <v>13</v>
+      </c>
+      <c r="H110">
+        <v>5</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.24549549549549549</v>
+      </c>
+      <c r="N110" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4639639639639639E-2</v>
+      </c>
+      <c r="O110" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.6306306306306304E-3</v>
+      </c>
+      <c r="P110" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.225563909774436</v>
+      </c>
+      <c r="Q110" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.54636591478696739</v>
+      </c>
+      <c r="R110" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.2581453634085211E-2</v>
+      </c>
+      <c r="S110" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.2531328320802004E-2</v>
+      </c>
+      <c r="T110" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1383</v>
+      </c>
+      <c r="U110" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.4661654135338344</v>
+      </c>
+      <c r="V110" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5574324324324325</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1</v>
+      </c>
+      <c r="C111" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D111" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>398</v>
+      </c>
+      <c r="E111" s="3">
+        <v>444</v>
+      </c>
+      <c r="F111">
+        <v>133</v>
+      </c>
+      <c r="G111">
+        <v>8</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29954954954954954</v>
+      </c>
+      <c r="N111" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.8018018018018018E-2</v>
+      </c>
+      <c r="O111" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2522522522522522E-3</v>
+      </c>
+      <c r="P111" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1155778894472361</v>
+      </c>
+      <c r="Q111" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.33417085427135679</v>
+      </c>
+      <c r="R111" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>2.0100502512562814E-2</v>
+      </c>
+      <c r="S111" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.5125628140703518E-3</v>
+      </c>
+      <c r="T111" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>738</v>
+      </c>
+      <c r="U111" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8542713567839195</v>
+      </c>
+      <c r="V111" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6621621621621621</v>
+      </c>
+    </row>
+    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C112" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D112" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>253</v>
+      </c>
+      <c r="E112" s="3">
+        <v>387</v>
+      </c>
+      <c r="F112">
+        <v>208</v>
+      </c>
+      <c r="G112">
+        <v>8</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.53746770025839796</v>
+      </c>
+      <c r="N112" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0671834625322998E-2</v>
+      </c>
+      <c r="O112" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.5839793281653748E-3</v>
+      </c>
+      <c r="P112" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5296442687747036</v>
+      </c>
+      <c r="Q112" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.82213438735177868</v>
+      </c>
+      <c r="R112" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.1620553359683792E-2</v>
+      </c>
+      <c r="S112" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.952569169960474E-3</v>
+      </c>
+      <c r="T112" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>831</v>
+      </c>
+      <c r="U112" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.2845849802371543</v>
+      </c>
+      <c r="V112" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1472868217054262</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B113" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D113" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>433</v>
+      </c>
+      <c r="E113" s="3">
+        <v>201</v>
+      </c>
+      <c r="F113">
+        <v>39</v>
+      </c>
+      <c r="G113">
+        <v>3</v>
+      </c>
+      <c r="H113">
+        <v>2</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19402985074626866</v>
+      </c>
+      <c r="N113" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4925373134328358E-2</v>
+      </c>
+      <c r="O113" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>9.9502487562189053E-3</v>
+      </c>
+      <c r="P113" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.46420323325635104</v>
+      </c>
+      <c r="Q113" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.0069284064665134E-2</v>
+      </c>
+      <c r="R113" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.9284064665127024E-3</v>
+      </c>
+      <c r="S113" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.6189376443418013E-3</v>
+      </c>
+      <c r="T113" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>296</v>
+      </c>
+      <c r="U113" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.68360277136258663</v>
+      </c>
+      <c r="V113" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.472636815920398</v>
+      </c>
+    </row>
+    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B114" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D114" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>251</v>
+      </c>
+      <c r="E114" s="3">
+        <v>198</v>
+      </c>
+      <c r="F114">
+        <v>25</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.12626262626262627</v>
+      </c>
+      <c r="N114" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>5.0505050505050509E-3</v>
+      </c>
+      <c r="O114" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.0505050505050509E-3</v>
+      </c>
+      <c r="P114" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.78884462151394419</v>
+      </c>
+      <c r="Q114" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.9601593625498003E-2</v>
+      </c>
+      <c r="R114" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="S114" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.9840637450199202E-3</v>
+      </c>
+      <c r="T114" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>255</v>
+      </c>
+      <c r="U114" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0159362549800797</v>
+      </c>
+      <c r="V114" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2878787878787878</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B115" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D115" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>149</v>
+      </c>
+      <c r="E115" s="3">
+        <v>146</v>
+      </c>
+      <c r="F115">
+        <v>82</v>
+      </c>
+      <c r="G115">
+        <v>2</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.56164383561643838</v>
+      </c>
+      <c r="N115" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.3698630136986301E-2</v>
+      </c>
+      <c r="O115" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P115" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.97986577181208057</v>
+      </c>
+      <c r="Q115" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.55033557046979864</v>
+      </c>
+      <c r="R115" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.3422818791946308E-2</v>
+      </c>
+      <c r="S115" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T115" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>316</v>
+      </c>
+      <c r="U115" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.1208053691275168</v>
+      </c>
+      <c r="V115" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1643835616438358</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:D7 D8:E1048576 C8:C73">
+  <conditionalFormatting sqref="C98:C115">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:D7 D98:E1048576 C8:E97">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E91 D1:D91 E98:E1048576 D92:E97">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F91 E1:E91 F98:F1048576 E92:F97">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:G91 F1:F91 G98:G1048576 F92:G97">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H115">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8:H91 G1:G91 H98:H1048576 G92:H97">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1:M1048576">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N115">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -6361,7 +10115,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E1048576 D1:D73">
+  <conditionalFormatting sqref="N8:N91 M1:M91 N98:N1048576 M92:N97">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O115">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6373,8 +10139,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F1048576 E1:E73">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="O8:O91 N1:N91 O98:O1048576 N92:O97">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6385,8 +10151,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G1048576 F1:F73">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="P2:P115">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6397,7 +10163,163 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H73">
+  <conditionalFormatting sqref="P8:Q91 O1:P91 P98:Q1048576 O92:Q97">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q115">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R115">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R8:R91 Q1:Q91 R98:R1048576 Q92:R97">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S115">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S8:S91 R1:R91 S98:S1048576 R92:S97">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T115">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T8:T91 S1:S91 T98:T1048576 S92:T97">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U115">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U8:U91 T1:T91 U98:U1048576 T92:U97">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V8:V91 U1:U91 V98:V1048576 U92:V97">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W8:W1048576 V1:V115">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F115">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G115">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6409,116 +10331,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H1048576 G1:G73">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N8:N1048576 M1:M73">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O1048576 N1:N73">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P8:Q1048576 O1:P73">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R8:R1048576 Q1:Q73">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S8:S1048576 R1:R73">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T1048576 S1:S73">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U8:U1048576 T1:T73">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V8:V1048576 U1:U73">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W1048576 V1:V73">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="C2:C115">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6534,4 +10348,4220 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2DEBD8-EF7F-4C29-BE2F-F33FA3B429D9}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.85546875" customWidth="1"/>
+    <col min="6" max="6" width="41.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>45784</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2">
+        <v>7031788</v>
+      </c>
+      <c r="F2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>45784</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3">
+        <v>7031806</v>
+      </c>
+      <c r="F3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>45784</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4">
+        <v>7031806</v>
+      </c>
+      <c r="F4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>45784</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5">
+        <v>7031806</v>
+      </c>
+      <c r="F5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>45784</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6">
+        <v>7031806</v>
+      </c>
+      <c r="F6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45784</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7">
+        <v>7031806</v>
+      </c>
+      <c r="F7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>45784</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8">
+        <v>7031806</v>
+      </c>
+      <c r="F8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>7031806</v>
+      </c>
+      <c r="F9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>45784</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10">
+        <v>7031806</v>
+      </c>
+      <c r="F10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <v>7031806</v>
+      </c>
+      <c r="F11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12">
+        <v>7054629</v>
+      </c>
+      <c r="F12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13">
+        <v>7054629</v>
+      </c>
+      <c r="F13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14">
+        <v>7054629</v>
+      </c>
+      <c r="F14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15">
+        <v>7054629</v>
+      </c>
+      <c r="F15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16">
+        <v>7054629</v>
+      </c>
+      <c r="F16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17">
+        <v>7054629</v>
+      </c>
+      <c r="F17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18">
+        <v>7054629</v>
+      </c>
+      <c r="F18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19">
+        <v>7054629</v>
+      </c>
+      <c r="F19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20">
+        <v>7054629</v>
+      </c>
+      <c r="F20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21">
+        <v>7054629</v>
+      </c>
+      <c r="F21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22">
+        <v>7054629</v>
+      </c>
+      <c r="F22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23">
+        <v>7054629</v>
+      </c>
+      <c r="F23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24">
+        <v>7054629</v>
+      </c>
+      <c r="F24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25">
+        <v>7054629</v>
+      </c>
+      <c r="F25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>45810</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26">
+        <v>7054629</v>
+      </c>
+      <c r="F26" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>45750</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27">
+        <v>6999906</v>
+      </c>
+      <c r="F27" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>45932</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28">
+        <v>7160565</v>
+      </c>
+      <c r="F28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29">
+        <v>7267989</v>
+      </c>
+      <c r="F29" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30">
+        <v>7267989</v>
+      </c>
+      <c r="F30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31">
+        <v>7267989</v>
+      </c>
+      <c r="F31" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32">
+        <v>7267989</v>
+      </c>
+      <c r="F32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33">
+        <v>7267989</v>
+      </c>
+      <c r="F33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34">
+        <v>7267989</v>
+      </c>
+      <c r="F34" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" t="s">
+        <v>98</v>
+      </c>
+      <c r="E35">
+        <v>7267989</v>
+      </c>
+      <c r="F35" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36">
+        <v>7267989</v>
+      </c>
+      <c r="F36" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37">
+        <v>7267989</v>
+      </c>
+      <c r="F37" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38">
+        <v>7267989</v>
+      </c>
+      <c r="F38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39">
+        <v>7267989</v>
+      </c>
+      <c r="F39" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" t="s">
+        <v>108</v>
+      </c>
+      <c r="E40">
+        <v>7267989</v>
+      </c>
+      <c r="F40" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41">
+        <v>7267989</v>
+      </c>
+      <c r="F41" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" t="s">
+        <v>112</v>
+      </c>
+      <c r="E42">
+        <v>7267989</v>
+      </c>
+      <c r="F42" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" t="s">
+        <v>114</v>
+      </c>
+      <c r="E43">
+        <v>7267989</v>
+      </c>
+      <c r="F43" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44">
+        <v>7267989</v>
+      </c>
+      <c r="F44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45">
+        <v>7267989</v>
+      </c>
+      <c r="F45" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46033</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E46">
+        <v>7267989</v>
+      </c>
+      <c r="F46" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" t="s">
+        <v>122</v>
+      </c>
+      <c r="E47">
+        <v>7267989</v>
+      </c>
+      <c r="F47" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC82DCFF-7BE9-4E03-A7FB-F5958C6B535A}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:D231"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>116</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>120</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>122</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>40</v>
+      </c>
+      <c r="D52">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>42</v>
+      </c>
+      <c r="D53">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D57">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>54</v>
+      </c>
+      <c r="D59">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>58</v>
+      </c>
+      <c r="D61">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>62</v>
+      </c>
+      <c r="D63">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D64">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>66</v>
+      </c>
+      <c r="D65">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>74</v>
+      </c>
+      <c r="D69">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>76</v>
+      </c>
+      <c r="D70">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>78</v>
+      </c>
+      <c r="D71">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" t="s">
+        <v>84</v>
+      </c>
+      <c r="D74">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
+        <v>86</v>
+      </c>
+      <c r="D75">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
+        <v>88</v>
+      </c>
+      <c r="D76">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>90</v>
+      </c>
+      <c r="D77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>92</v>
+      </c>
+      <c r="D78">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>94</v>
+      </c>
+      <c r="D79">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>96</v>
+      </c>
+      <c r="D80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>98</v>
+      </c>
+      <c r="D81">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>102</v>
+      </c>
+      <c r="D83">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>104</v>
+      </c>
+      <c r="D84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>106</v>
+      </c>
+      <c r="D85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B86" t="s">
+        <v>4</v>
+      </c>
+      <c r="C86" t="s">
+        <v>108</v>
+      </c>
+      <c r="D86">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>110</v>
+      </c>
+      <c r="D87">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>116</v>
+      </c>
+      <c r="D90">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>118</v>
+      </c>
+      <c r="D91">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>120</v>
+      </c>
+      <c r="D92">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>122</v>
+      </c>
+      <c r="D93">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B94" t="s">
+        <v>0</v>
+      </c>
+      <c r="C94" t="s">
+        <v>32</v>
+      </c>
+      <c r="D94">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" t="s">
+        <v>36</v>
+      </c>
+      <c r="D96">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1</v>
+      </c>
+      <c r="C97" t="s">
+        <v>38</v>
+      </c>
+      <c r="D97">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>40</v>
+      </c>
+      <c r="D98">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>42</v>
+      </c>
+      <c r="D99">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
+        <v>46</v>
+      </c>
+      <c r="D101">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>48</v>
+      </c>
+      <c r="D102">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>50</v>
+      </c>
+      <c r="D103">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B104" t="s">
+        <v>2</v>
+      </c>
+      <c r="C104" t="s">
+        <v>52</v>
+      </c>
+      <c r="D104">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B105" t="s">
+        <v>2</v>
+      </c>
+      <c r="C105" t="s">
+        <v>54</v>
+      </c>
+      <c r="D105">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B106" t="s">
+        <v>2</v>
+      </c>
+      <c r="C106" t="s">
+        <v>56</v>
+      </c>
+      <c r="D106">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B107" t="s">
+        <v>2</v>
+      </c>
+      <c r="C107" t="s">
+        <v>58</v>
+      </c>
+      <c r="D107">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B108" t="s">
+        <v>2</v>
+      </c>
+      <c r="C108" t="s">
+        <v>60</v>
+      </c>
+      <c r="D108">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B109" t="s">
+        <v>2</v>
+      </c>
+      <c r="C109" t="s">
+        <v>62</v>
+      </c>
+      <c r="D109">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B110" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" t="s">
+        <v>64</v>
+      </c>
+      <c r="D110">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>66</v>
+      </c>
+      <c r="D111">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B113" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" t="s">
+        <v>70</v>
+      </c>
+      <c r="D113">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B114" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" t="s">
+        <v>72</v>
+      </c>
+      <c r="D114">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B115" t="s">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>74</v>
+      </c>
+      <c r="D115">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B116" t="s">
+        <v>2</v>
+      </c>
+      <c r="C116" t="s">
+        <v>76</v>
+      </c>
+      <c r="D116">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B117" t="s">
+        <v>2</v>
+      </c>
+      <c r="C117" t="s">
+        <v>78</v>
+      </c>
+      <c r="D117">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B118" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" t="s">
+        <v>80</v>
+      </c>
+      <c r="D118">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B119" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" t="s">
+        <v>82</v>
+      </c>
+      <c r="D119">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B120" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" t="s">
+        <v>84</v>
+      </c>
+      <c r="D120">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B121" t="s">
+        <v>4</v>
+      </c>
+      <c r="C121" t="s">
+        <v>86</v>
+      </c>
+      <c r="D121">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B122" t="s">
+        <v>4</v>
+      </c>
+      <c r="C122" t="s">
+        <v>88</v>
+      </c>
+      <c r="D122">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B123" t="s">
+        <v>4</v>
+      </c>
+      <c r="C123" t="s">
+        <v>90</v>
+      </c>
+      <c r="D123">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4</v>
+      </c>
+      <c r="C124" t="s">
+        <v>92</v>
+      </c>
+      <c r="D124">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B125" t="s">
+        <v>4</v>
+      </c>
+      <c r="C125" t="s">
+        <v>94</v>
+      </c>
+      <c r="D125">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B126" t="s">
+        <v>4</v>
+      </c>
+      <c r="C126" t="s">
+        <v>96</v>
+      </c>
+      <c r="D126">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B127" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127" t="s">
+        <v>98</v>
+      </c>
+      <c r="D127">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B128" t="s">
+        <v>4</v>
+      </c>
+      <c r="C128" t="s">
+        <v>100</v>
+      </c>
+      <c r="D128">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B129" t="s">
+        <v>4</v>
+      </c>
+      <c r="C129" t="s">
+        <v>102</v>
+      </c>
+      <c r="D129">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B130" t="s">
+        <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>104</v>
+      </c>
+      <c r="D130">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B131" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" t="s">
+        <v>106</v>
+      </c>
+      <c r="D131">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B132" t="s">
+        <v>4</v>
+      </c>
+      <c r="C132" t="s">
+        <v>108</v>
+      </c>
+      <c r="D132">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B133" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>110</v>
+      </c>
+      <c r="D133">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B134" t="s">
+        <v>4</v>
+      </c>
+      <c r="C134" t="s">
+        <v>112</v>
+      </c>
+      <c r="D134">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B135" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" t="s">
+        <v>114</v>
+      </c>
+      <c r="D135">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B136" t="s">
+        <v>4</v>
+      </c>
+      <c r="C136" t="s">
+        <v>116</v>
+      </c>
+      <c r="D136">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B137" t="s">
+        <v>4</v>
+      </c>
+      <c r="C137" t="s">
+        <v>118</v>
+      </c>
+      <c r="D137">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B138" t="s">
+        <v>4</v>
+      </c>
+      <c r="C138" t="s">
+        <v>120</v>
+      </c>
+      <c r="D138">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B139" t="s">
+        <v>4</v>
+      </c>
+      <c r="C139" t="s">
+        <v>122</v>
+      </c>
+      <c r="D139">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B140" t="s">
+        <v>0</v>
+      </c>
+      <c r="C140" t="s">
+        <v>32</v>
+      </c>
+      <c r="D140">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1</v>
+      </c>
+      <c r="C141" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1</v>
+      </c>
+      <c r="C142" t="s">
+        <v>36</v>
+      </c>
+      <c r="D142">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1</v>
+      </c>
+      <c r="C143" t="s">
+        <v>38</v>
+      </c>
+      <c r="D143">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1</v>
+      </c>
+      <c r="C144" t="s">
+        <v>40</v>
+      </c>
+      <c r="D144">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1</v>
+      </c>
+      <c r="C145" t="s">
+        <v>42</v>
+      </c>
+      <c r="D145">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1</v>
+      </c>
+      <c r="C146" t="s">
+        <v>44</v>
+      </c>
+      <c r="D146">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1</v>
+      </c>
+      <c r="C147" t="s">
+        <v>46</v>
+      </c>
+      <c r="D147">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1</v>
+      </c>
+      <c r="C148" t="s">
+        <v>48</v>
+      </c>
+      <c r="D148">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1</v>
+      </c>
+      <c r="C149" t="s">
+        <v>50</v>
+      </c>
+      <c r="D149">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B150" t="s">
+        <v>2</v>
+      </c>
+      <c r="C150" t="s">
+        <v>52</v>
+      </c>
+      <c r="D150">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B151" t="s">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>54</v>
+      </c>
+      <c r="D151">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B152" t="s">
+        <v>2</v>
+      </c>
+      <c r="C152" t="s">
+        <v>56</v>
+      </c>
+      <c r="D152">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B153" t="s">
+        <v>2</v>
+      </c>
+      <c r="C153" t="s">
+        <v>58</v>
+      </c>
+      <c r="D153">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C154" t="s">
+        <v>60</v>
+      </c>
+      <c r="D154">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B155" t="s">
+        <v>2</v>
+      </c>
+      <c r="C155" t="s">
+        <v>62</v>
+      </c>
+      <c r="D155">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B156" t="s">
+        <v>2</v>
+      </c>
+      <c r="C156" t="s">
+        <v>64</v>
+      </c>
+      <c r="D156">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B157" t="s">
+        <v>2</v>
+      </c>
+      <c r="C157" t="s">
+        <v>66</v>
+      </c>
+      <c r="D157">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B158" t="s">
+        <v>2</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B159" t="s">
+        <v>2</v>
+      </c>
+      <c r="C159" t="s">
+        <v>70</v>
+      </c>
+      <c r="D159">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B160" t="s">
+        <v>2</v>
+      </c>
+      <c r="C160" t="s">
+        <v>72</v>
+      </c>
+      <c r="D160">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B161" t="s">
+        <v>2</v>
+      </c>
+      <c r="C161" t="s">
+        <v>74</v>
+      </c>
+      <c r="D161">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B162" t="s">
+        <v>2</v>
+      </c>
+      <c r="C162" t="s">
+        <v>76</v>
+      </c>
+      <c r="D162">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B163" t="s">
+        <v>2</v>
+      </c>
+      <c r="C163" t="s">
+        <v>78</v>
+      </c>
+      <c r="D163">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B164" t="s">
+        <v>2</v>
+      </c>
+      <c r="C164" t="s">
+        <v>80</v>
+      </c>
+      <c r="D164">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B165" t="s">
+        <v>13</v>
+      </c>
+      <c r="C165" t="s">
+        <v>82</v>
+      </c>
+      <c r="D165">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B166" t="s">
+        <v>3</v>
+      </c>
+      <c r="C166" t="s">
+        <v>84</v>
+      </c>
+      <c r="D166">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B167" t="s">
+        <v>4</v>
+      </c>
+      <c r="C167" t="s">
+        <v>86</v>
+      </c>
+      <c r="D167">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B168" t="s">
+        <v>4</v>
+      </c>
+      <c r="C168" t="s">
+        <v>88</v>
+      </c>
+      <c r="D168">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B169" t="s">
+        <v>4</v>
+      </c>
+      <c r="C169" t="s">
+        <v>90</v>
+      </c>
+      <c r="D169">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B170" t="s">
+        <v>4</v>
+      </c>
+      <c r="C170" t="s">
+        <v>92</v>
+      </c>
+      <c r="D170">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B171" t="s">
+        <v>4</v>
+      </c>
+      <c r="C171" t="s">
+        <v>94</v>
+      </c>
+      <c r="D171">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B172" t="s">
+        <v>4</v>
+      </c>
+      <c r="C172" t="s">
+        <v>96</v>
+      </c>
+      <c r="D172">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B173" t="s">
+        <v>4</v>
+      </c>
+      <c r="C173" t="s">
+        <v>98</v>
+      </c>
+      <c r="D173">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B174" t="s">
+        <v>4</v>
+      </c>
+      <c r="C174" t="s">
+        <v>100</v>
+      </c>
+      <c r="D174">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B175" t="s">
+        <v>4</v>
+      </c>
+      <c r="C175" t="s">
+        <v>102</v>
+      </c>
+      <c r="D175">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B176" t="s">
+        <v>4</v>
+      </c>
+      <c r="C176" t="s">
+        <v>104</v>
+      </c>
+      <c r="D176">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>4</v>
+      </c>
+      <c r="C177" t="s">
+        <v>106</v>
+      </c>
+      <c r="D177">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B178" t="s">
+        <v>4</v>
+      </c>
+      <c r="C178" t="s">
+        <v>108</v>
+      </c>
+      <c r="D178">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B179" t="s">
+        <v>4</v>
+      </c>
+      <c r="C179" t="s">
+        <v>110</v>
+      </c>
+      <c r="D179">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B180" t="s">
+        <v>4</v>
+      </c>
+      <c r="C180" t="s">
+        <v>112</v>
+      </c>
+      <c r="D180">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B181" t="s">
+        <v>4</v>
+      </c>
+      <c r="C181" t="s">
+        <v>114</v>
+      </c>
+      <c r="D181">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B182" t="s">
+        <v>4</v>
+      </c>
+      <c r="C182" t="s">
+        <v>116</v>
+      </c>
+      <c r="D182">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B183" t="s">
+        <v>4</v>
+      </c>
+      <c r="C183" t="s">
+        <v>118</v>
+      </c>
+      <c r="D183">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B184" t="s">
+        <v>4</v>
+      </c>
+      <c r="C184" t="s">
+        <v>120</v>
+      </c>
+      <c r="D184">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B185" t="s">
+        <v>4</v>
+      </c>
+      <c r="C185" t="s">
+        <v>122</v>
+      </c>
+      <c r="D185">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B186" t="s">
+        <v>0</v>
+      </c>
+      <c r="C186" t="s">
+        <v>32</v>
+      </c>
+      <c r="D186">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1</v>
+      </c>
+      <c r="C187" t="s">
+        <v>34</v>
+      </c>
+      <c r="D187">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1</v>
+      </c>
+      <c r="C188" t="s">
+        <v>36</v>
+      </c>
+      <c r="D188">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1</v>
+      </c>
+      <c r="C189" t="s">
+        <v>38</v>
+      </c>
+      <c r="D189">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1</v>
+      </c>
+      <c r="C190" t="s">
+        <v>40</v>
+      </c>
+      <c r="D190">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1</v>
+      </c>
+      <c r="C191" t="s">
+        <v>42</v>
+      </c>
+      <c r="D191">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1</v>
+      </c>
+      <c r="C192" t="s">
+        <v>44</v>
+      </c>
+      <c r="D192">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1</v>
+      </c>
+      <c r="C193" t="s">
+        <v>46</v>
+      </c>
+      <c r="D193">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1</v>
+      </c>
+      <c r="C194" t="s">
+        <v>48</v>
+      </c>
+      <c r="D194">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1</v>
+      </c>
+      <c r="C195" t="s">
+        <v>50</v>
+      </c>
+      <c r="D195">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B196" t="s">
+        <v>2</v>
+      </c>
+      <c r="C196" t="s">
+        <v>52</v>
+      </c>
+      <c r="D196">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B197" t="s">
+        <v>2</v>
+      </c>
+      <c r="C197" t="s">
+        <v>54</v>
+      </c>
+      <c r="D197">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B198" t="s">
+        <v>2</v>
+      </c>
+      <c r="C198" t="s">
+        <v>56</v>
+      </c>
+      <c r="D198">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B199" t="s">
+        <v>2</v>
+      </c>
+      <c r="C199" t="s">
+        <v>58</v>
+      </c>
+      <c r="D199">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B200" t="s">
+        <v>2</v>
+      </c>
+      <c r="C200" t="s">
+        <v>60</v>
+      </c>
+      <c r="D200">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B201" t="s">
+        <v>2</v>
+      </c>
+      <c r="C201" t="s">
+        <v>62</v>
+      </c>
+      <c r="D201">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B202" t="s">
+        <v>2</v>
+      </c>
+      <c r="C202" t="s">
+        <v>64</v>
+      </c>
+      <c r="D202">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B203" t="s">
+        <v>2</v>
+      </c>
+      <c r="C203" t="s">
+        <v>66</v>
+      </c>
+      <c r="D203">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B204" t="s">
+        <v>2</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B205" t="s">
+        <v>2</v>
+      </c>
+      <c r="C205" t="s">
+        <v>70</v>
+      </c>
+      <c r="D205">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B206" t="s">
+        <v>2</v>
+      </c>
+      <c r="C206" t="s">
+        <v>72</v>
+      </c>
+      <c r="D206">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B207" t="s">
+        <v>2</v>
+      </c>
+      <c r="C207" t="s">
+        <v>74</v>
+      </c>
+      <c r="D207">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B208" t="s">
+        <v>2</v>
+      </c>
+      <c r="C208" t="s">
+        <v>76</v>
+      </c>
+      <c r="D208">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B209" t="s">
+        <v>2</v>
+      </c>
+      <c r="C209" t="s">
+        <v>78</v>
+      </c>
+      <c r="D209">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B210" t="s">
+        <v>2</v>
+      </c>
+      <c r="C210" t="s">
+        <v>80</v>
+      </c>
+      <c r="D210">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B211" t="s">
+        <v>13</v>
+      </c>
+      <c r="C211" t="s">
+        <v>82</v>
+      </c>
+      <c r="D211">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B212" t="s">
+        <v>3</v>
+      </c>
+      <c r="C212" t="s">
+        <v>84</v>
+      </c>
+      <c r="D212">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B213" t="s">
+        <v>4</v>
+      </c>
+      <c r="C213" t="s">
+        <v>86</v>
+      </c>
+      <c r="D213">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B214" t="s">
+        <v>4</v>
+      </c>
+      <c r="C214" t="s">
+        <v>88</v>
+      </c>
+      <c r="D214">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B215" t="s">
+        <v>4</v>
+      </c>
+      <c r="C215" t="s">
+        <v>90</v>
+      </c>
+      <c r="D215">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B216" t="s">
+        <v>4</v>
+      </c>
+      <c r="C216" t="s">
+        <v>92</v>
+      </c>
+      <c r="D216">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B217" t="s">
+        <v>4</v>
+      </c>
+      <c r="C217" t="s">
+        <v>94</v>
+      </c>
+      <c r="D217">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B218" t="s">
+        <v>4</v>
+      </c>
+      <c r="C218" t="s">
+        <v>96</v>
+      </c>
+      <c r="D218">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B219" t="s">
+        <v>4</v>
+      </c>
+      <c r="C219" t="s">
+        <v>98</v>
+      </c>
+      <c r="D219">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B220" t="s">
+        <v>4</v>
+      </c>
+      <c r="C220" t="s">
+        <v>100</v>
+      </c>
+      <c r="D220">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B221" t="s">
+        <v>4</v>
+      </c>
+      <c r="C221" t="s">
+        <v>102</v>
+      </c>
+      <c r="D221">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B222" t="s">
+        <v>4</v>
+      </c>
+      <c r="C222" t="s">
+        <v>104</v>
+      </c>
+      <c r="D222">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B223" t="s">
+        <v>4</v>
+      </c>
+      <c r="C223" t="s">
+        <v>106</v>
+      </c>
+      <c r="D223">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B224" t="s">
+        <v>4</v>
+      </c>
+      <c r="C224" t="s">
+        <v>108</v>
+      </c>
+      <c r="D224">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B225" t="s">
+        <v>4</v>
+      </c>
+      <c r="C225" t="s">
+        <v>110</v>
+      </c>
+      <c r="D225">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B226" t="s">
+        <v>4</v>
+      </c>
+      <c r="C226" t="s">
+        <v>112</v>
+      </c>
+      <c r="D226">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B227" t="s">
+        <v>4</v>
+      </c>
+      <c r="C227" t="s">
+        <v>114</v>
+      </c>
+      <c r="D227">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B228" t="s">
+        <v>4</v>
+      </c>
+      <c r="C228" t="s">
+        <v>116</v>
+      </c>
+      <c r="D228">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B229" t="s">
+        <v>4</v>
+      </c>
+      <c r="C229" t="s">
+        <v>118</v>
+      </c>
+      <c r="D229">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B230" t="s">
+        <v>4</v>
+      </c>
+      <c r="C230" t="s">
+        <v>120</v>
+      </c>
+      <c r="D230">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B231" t="s">
+        <v>4</v>
+      </c>
+      <c r="C231" t="s">
+        <v>122</v>
+      </c>
+      <c r="D231">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Python/Thingiverse/model_stats.xlsx
+++ b/Python/Thingiverse/model_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Thingiverse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923F3EBE-0887-4658-9D72-DC860D8DDAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256543C0-04A6-4D05-A7C2-7EE0687CBC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
+    <workbookView xWindow="24090" yWindow="6420" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{AA65E66E-25AF-41FC-AF3D-E4037625FDAB}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="131">
   <si>
     <t>Mammoth</t>
   </si>
@@ -522,8 +522,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V115" totalsRowShown="0">
-  <autoFilter ref="A1:V115" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}" name="Table1" displayName="Table1" ref="A1:V127" totalsRowShown="0">
+  <autoFilter ref="A1:V127" xr:uid="{83CFD035-DF42-4179-A65F-EE1B5D7828A5}"/>
   <tableColumns count="22">
     <tableColumn id="22" xr3:uid="{B838C6CD-92E8-4070-81DB-2EDE900509A2}" name="Date"/>
     <tableColumn id="1" xr3:uid="{C06BFB11-D5FB-45F8-853C-B38F6CA36FF6}" name="Model"/>
@@ -590,8 +590,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BB676C2C-B3FE-42B4-A6C0-059962FBB89A}" name="Table2" displayName="Table2" ref="A1:D231" totalsRowShown="0">
-  <autoFilter ref="A1:D231" xr:uid="{BB676C2C-B3FE-42B4-A6C0-059962FBB89A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BB676C2C-B3FE-42B4-A6C0-059962FBB89A}" name="Table2" displayName="Table2" ref="A1:D323" totalsRowShown="0">
+  <autoFilter ref="A1:D323" xr:uid="{BB676C2C-B3FE-42B4-A6C0-059962FBB89A}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{E9D80D2D-BB1D-4FDE-90CE-06D854D914ED}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{84AE994F-16AA-4683-9C1D-6B8C3F098F6A}" name="Parent"/>
@@ -900,7 +900,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC85C3B-1FD4-46FE-8A2F-07E281673B93}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:W115"/>
+  <dimension ref="A1:W127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -10008,8 +10008,968 @@
         <v>2.1643835616438358</v>
       </c>
     </row>
+    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B116" t="s">
+        <v>0</v>
+      </c>
+      <c r="C116" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D116" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>406</v>
+      </c>
+      <c r="E116" s="3">
+        <v>899</v>
+      </c>
+      <c r="F116">
+        <v>220</v>
+      </c>
+      <c r="G116">
+        <v>13</v>
+      </c>
+      <c r="H116">
+        <v>5</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.24471635150166851</v>
+      </c>
+      <c r="N116" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4460511679644048E-2</v>
+      </c>
+      <c r="O116" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.5617352614015575E-3</v>
+      </c>
+      <c r="P116" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2142857142857144</v>
+      </c>
+      <c r="Q116" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.54187192118226601</v>
+      </c>
+      <c r="R116" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.2019704433497539E-2</v>
+      </c>
+      <c r="S116" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.2315270935960592E-2</v>
+      </c>
+      <c r="T116" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1398</v>
+      </c>
+      <c r="U116" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.4433497536945814</v>
+      </c>
+      <c r="V116" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5550611790878754</v>
+      </c>
+    </row>
+    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1</v>
+      </c>
+      <c r="C117" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D117" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>405</v>
+      </c>
+      <c r="E117" s="3">
+        <v>447</v>
+      </c>
+      <c r="F117">
+        <v>133</v>
+      </c>
+      <c r="G117">
+        <v>8</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29753914988814317</v>
+      </c>
+      <c r="N117" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7897091722595078E-2</v>
+      </c>
+      <c r="O117" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2371364653243847E-3</v>
+      </c>
+      <c r="P117" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.1037037037037036</v>
+      </c>
+      <c r="Q117" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.32839506172839505</v>
+      </c>
+      <c r="R117" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.9753086419753086E-2</v>
+      </c>
+      <c r="S117" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.4691358024691358E-3</v>
+      </c>
+      <c r="T117" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>741</v>
+      </c>
+      <c r="U117" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8296296296296297</v>
+      </c>
+      <c r="V117" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6577181208053691</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B118" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D118" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>260</v>
+      </c>
+      <c r="E118" s="3">
+        <v>404</v>
+      </c>
+      <c r="F118">
+        <v>209</v>
+      </c>
+      <c r="G118">
+        <v>8</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.51732673267326734</v>
+      </c>
+      <c r="N118" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9801980198019802E-2</v>
+      </c>
+      <c r="O118" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.4752475247524753E-3</v>
+      </c>
+      <c r="P118" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5538461538461539</v>
+      </c>
+      <c r="Q118" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.80384615384615388</v>
+      </c>
+      <c r="R118" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.0769230769230771E-2</v>
+      </c>
+      <c r="S118" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.8461538461538464E-3</v>
+      </c>
+      <c r="T118" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>850</v>
+      </c>
+      <c r="U118" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.2692307692307692</v>
+      </c>
+      <c r="V118" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1039603960396041</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B119" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D119" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>440</v>
+      </c>
+      <c r="E119" s="3">
+        <v>202</v>
+      </c>
+      <c r="F119">
+        <v>39</v>
+      </c>
+      <c r="G119">
+        <v>3</v>
+      </c>
+      <c r="H119">
+        <v>2</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.19306930693069307</v>
+      </c>
+      <c r="N119" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4851485148514851E-2</v>
+      </c>
+      <c r="O119" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="P119" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.45909090909090911</v>
+      </c>
+      <c r="Q119" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.8636363636363638E-2</v>
+      </c>
+      <c r="R119" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.8181818181818179E-3</v>
+      </c>
+      <c r="S119" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.5454545454545452E-3</v>
+      </c>
+      <c r="T119" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>297</v>
+      </c>
+      <c r="U119" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="V119" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4702970297029703</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B120" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D120" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>258</v>
+      </c>
+      <c r="E120" s="3">
+        <v>209</v>
+      </c>
+      <c r="F120">
+        <v>25</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.11961722488038277</v>
+      </c>
+      <c r="N120" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>4.7846889952153108E-3</v>
+      </c>
+      <c r="O120" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>4.7846889952153108E-3</v>
+      </c>
+      <c r="P120" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.81007751937984496</v>
+      </c>
+      <c r="Q120" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.6899224806201556E-2</v>
+      </c>
+      <c r="R120" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.875968992248062E-3</v>
+      </c>
+      <c r="S120" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.875968992248062E-3</v>
+      </c>
+      <c r="T120" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>266</v>
+      </c>
+      <c r="U120" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0310077519379846</v>
+      </c>
+      <c r="V120" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2727272727272727</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B121" t="s">
+        <v>4</v>
+      </c>
+      <c r="C121" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D121" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>156</v>
+      </c>
+      <c r="E121" s="3">
+        <v>149</v>
+      </c>
+      <c r="F121">
+        <v>82</v>
+      </c>
+      <c r="G121">
+        <v>2</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.55033557046979864</v>
+      </c>
+      <c r="N121" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.3422818791946308E-2</v>
+      </c>
+      <c r="O121" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P121" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.95512820512820518</v>
+      </c>
+      <c r="Q121" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.52564102564102566</v>
+      </c>
+      <c r="R121" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.282051282051282E-2</v>
+      </c>
+      <c r="S121" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T121" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>319</v>
+      </c>
+      <c r="U121" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>2.0448717948717947</v>
+      </c>
+      <c r="V121" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1409395973154361</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B122" t="s">
+        <v>0</v>
+      </c>
+      <c r="C122" s="1">
+        <v>45784</v>
+      </c>
+      <c r="D122" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>412</v>
+      </c>
+      <c r="E122" s="3">
+        <v>909</v>
+      </c>
+      <c r="F122">
+        <v>221</v>
+      </c>
+      <c r="G122">
+        <v>13</v>
+      </c>
+      <c r="H122">
+        <v>5</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.24312431243124313</v>
+      </c>
+      <c r="N122" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.4301430143014302E-2</v>
+      </c>
+      <c r="O122" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.5005500550055009E-3</v>
+      </c>
+      <c r="P122" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>2.2063106796116503</v>
+      </c>
+      <c r="Q122" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.53640776699029125</v>
+      </c>
+      <c r="R122" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.1553398058252427E-2</v>
+      </c>
+      <c r="S122" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>1.2135922330097087E-2</v>
+      </c>
+      <c r="T122" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>1410</v>
+      </c>
+      <c r="U122" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.4223300970873787</v>
+      </c>
+      <c r="V122" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.5511551155115511</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123" s="1">
+        <v>45785</v>
+      </c>
+      <c r="D123" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>411</v>
+      </c>
+      <c r="E123" s="3">
+        <v>451</v>
+      </c>
+      <c r="F123">
+        <v>134</v>
+      </c>
+      <c r="G123">
+        <v>8</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.29711751662971175</v>
+      </c>
+      <c r="N123" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.7738359201773836E-2</v>
+      </c>
+      <c r="O123" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.2172949002217295E-3</v>
+      </c>
+      <c r="P123" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0973236009732361</v>
+      </c>
+      <c r="Q123" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.32603406326034062</v>
+      </c>
+      <c r="R123" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.9464720194647202E-2</v>
+      </c>
+      <c r="S123" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>2.4330900243309003E-3</v>
+      </c>
+      <c r="T123" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>747</v>
+      </c>
+      <c r="U123" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.8175182481751824</v>
+      </c>
+      <c r="V123" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.6563192904656319</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B124" t="s">
+        <v>2</v>
+      </c>
+      <c r="C124" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D124" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>266</v>
+      </c>
+      <c r="E124" s="3">
+        <v>411</v>
+      </c>
+      <c r="F124">
+        <v>211</v>
+      </c>
+      <c r="G124">
+        <v>8</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.51338199513381999</v>
+      </c>
+      <c r="N124" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.9464720194647202E-2</v>
+      </c>
+      <c r="O124" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>2.4330900243309003E-3</v>
+      </c>
+      <c r="P124" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>1.5451127819548873</v>
+      </c>
+      <c r="Q124" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.79323308270676696</v>
+      </c>
+      <c r="R124" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.007518796992481E-2</v>
+      </c>
+      <c r="S124" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.7593984962406013E-3</v>
+      </c>
+      <c r="T124" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>861</v>
+      </c>
+      <c r="U124" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>3.236842105263158</v>
+      </c>
+      <c r="V124" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.0948905109489053</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B125" t="s">
+        <v>13</v>
+      </c>
+      <c r="C125" s="1">
+        <v>45750</v>
+      </c>
+      <c r="D125" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>446</v>
+      </c>
+      <c r="E125" s="3">
+        <v>39</v>
+      </c>
+      <c r="F125">
+        <v>39</v>
+      </c>
+      <c r="G125">
+        <v>3</v>
+      </c>
+      <c r="H125">
+        <v>2</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>1</v>
+      </c>
+      <c r="N125" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="O125" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>5.128205128205128E-2</v>
+      </c>
+      <c r="P125" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>8.744394618834081E-2</v>
+      </c>
+      <c r="Q125" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>8.744394618834081E-2</v>
+      </c>
+      <c r="R125" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>6.7264573991031393E-3</v>
+      </c>
+      <c r="S125" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>4.4843049327354259E-3</v>
+      </c>
+      <c r="T125" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>134</v>
+      </c>
+      <c r="U125" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>0.30044843049327352</v>
+      </c>
+      <c r="V125" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>3.4358974358974357</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B126" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D126" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>264</v>
+      </c>
+      <c r="E126" s="3">
+        <v>216</v>
+      </c>
+      <c r="F126">
+        <v>25</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.11574074074074074</v>
+      </c>
+      <c r="N126" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>4.6296296296296294E-3</v>
+      </c>
+      <c r="O126" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>4.6296296296296294E-3</v>
+      </c>
+      <c r="P126" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="Q126" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>9.4696969696969696E-2</v>
+      </c>
+      <c r="R126" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>3.787878787878788E-3</v>
+      </c>
+      <c r="S126" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>3.787878787878788E-3</v>
+      </c>
+      <c r="T126" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>273</v>
+      </c>
+      <c r="U126" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.0340909090909092</v>
+      </c>
+      <c r="V126" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>1.2638888888888888</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B127" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D127" s="2">
+        <f>Table1[[#This Row],[Date]]-Table1[[#This Row],[Published]]</f>
+        <v>162</v>
+      </c>
+      <c r="E127" s="3">
+        <v>153</v>
+      </c>
+      <c r="F127">
+        <v>82</v>
+      </c>
+      <c r="G127">
+        <v>2</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Views]]</f>
+        <v>0.53594771241830064</v>
+      </c>
+      <c r="N127" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Views]]</f>
+        <v>1.3071895424836602E-2</v>
+      </c>
+      <c r="O127" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Views]]</f>
+        <v>0</v>
+      </c>
+      <c r="P127" s="4">
+        <f>Table1[[#This Row],[Views]]/Table1[[#This Row],[Age]]</f>
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="Q127" s="4">
+        <f>Table1[[#This Row],[Downloads]]/Table1[[#This Row],[Age]]</f>
+        <v>0.50617283950617287</v>
+      </c>
+      <c r="R127" s="4">
+        <f>Table1[[#This Row],[Likes]]/Table1[[#This Row],[Age]]</f>
+        <v>1.2345679012345678E-2</v>
+      </c>
+      <c r="S127" s="4">
+        <f>Table1[[#This Row],[Collects]]/Table1[[#This Row],[Age]]</f>
+        <v>0</v>
+      </c>
+      <c r="T127" s="4">
+        <f>(4*Table1[[#This Row],[Collects]])+(3*Table1[[#This Row],[Likes]])+(2*Table1[[#This Row],[Downloads]])+Table1[[#This Row],[Views]]</f>
+        <v>323</v>
+      </c>
+      <c r="U127" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Age]]</f>
+        <v>1.9938271604938271</v>
+      </c>
+      <c r="V127" s="4">
+        <f>Table1[[#This Row],[Score]]/Table1[[#This Row],[Views]]</f>
+        <v>2.1111111111111112</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C98:C115">
+  <conditionalFormatting sqref="C2:C127">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C98:C127">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -10045,8 +11005,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F127">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F8:F91 E1:E91 F98:F1048576 E92:F97">
     <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G127">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10069,7 +11053,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H115">
+  <conditionalFormatting sqref="H1:H127">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -10103,7 +11087,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N115">
+  <conditionalFormatting sqref="N2:N127">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -10127,7 +11111,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O115">
+  <conditionalFormatting sqref="O2:O127">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -10151,7 +11135,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P115">
+  <conditionalFormatting sqref="P2:P127">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -10175,7 +11159,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q115">
+  <conditionalFormatting sqref="Q2:Q127">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -10187,7 +11171,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R115">
+  <conditionalFormatting sqref="R2:R127">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -10211,7 +11195,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S115">
+  <conditionalFormatting sqref="S2:S127">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -10235,7 +11219,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T115">
+  <conditionalFormatting sqref="T2:T127">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -10259,7 +11243,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U115">
+  <conditionalFormatting sqref="U2:U127">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -10295,44 +11279,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W8:W1048576 V1:V115">
+  <conditionalFormatting sqref="W8:W1048576 V1:V127">
     <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F115">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G115">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C115">
-    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11315,7 +12263,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC82DCFF-7BE9-4E03-A7FB-F5958C6B535A}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D323"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -14558,6 +15506,1294 @@
         <v>10</v>
       </c>
     </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B232" t="s">
+        <v>0</v>
+      </c>
+      <c r="C232" t="s">
+        <v>32</v>
+      </c>
+      <c r="D232">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1</v>
+      </c>
+      <c r="C233" t="s">
+        <v>34</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1</v>
+      </c>
+      <c r="C234" t="s">
+        <v>36</v>
+      </c>
+      <c r="D234">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1</v>
+      </c>
+      <c r="C235" t="s">
+        <v>38</v>
+      </c>
+      <c r="D235">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1</v>
+      </c>
+      <c r="C236" t="s">
+        <v>40</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1</v>
+      </c>
+      <c r="C237" t="s">
+        <v>42</v>
+      </c>
+      <c r="D237">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1</v>
+      </c>
+      <c r="C238" t="s">
+        <v>44</v>
+      </c>
+      <c r="D238">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1</v>
+      </c>
+      <c r="C239" t="s">
+        <v>46</v>
+      </c>
+      <c r="D239">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B240" t="s">
+        <v>1</v>
+      </c>
+      <c r="C240" t="s">
+        <v>48</v>
+      </c>
+      <c r="D240">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1</v>
+      </c>
+      <c r="C241" t="s">
+        <v>50</v>
+      </c>
+      <c r="D241">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B242" t="s">
+        <v>2</v>
+      </c>
+      <c r="C242" t="s">
+        <v>52</v>
+      </c>
+      <c r="D242">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B243" t="s">
+        <v>2</v>
+      </c>
+      <c r="C243" t="s">
+        <v>54</v>
+      </c>
+      <c r="D243">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B244" t="s">
+        <v>2</v>
+      </c>
+      <c r="C244" t="s">
+        <v>56</v>
+      </c>
+      <c r="D244">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B245" t="s">
+        <v>2</v>
+      </c>
+      <c r="C245" t="s">
+        <v>58</v>
+      </c>
+      <c r="D245">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B246" t="s">
+        <v>2</v>
+      </c>
+      <c r="C246" t="s">
+        <v>60</v>
+      </c>
+      <c r="D246">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B247" t="s">
+        <v>2</v>
+      </c>
+      <c r="C247" t="s">
+        <v>62</v>
+      </c>
+      <c r="D247">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B248" t="s">
+        <v>2</v>
+      </c>
+      <c r="C248" t="s">
+        <v>64</v>
+      </c>
+      <c r="D248">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B249" t="s">
+        <v>2</v>
+      </c>
+      <c r="C249" t="s">
+        <v>66</v>
+      </c>
+      <c r="D249">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B250" t="s">
+        <v>2</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B251" t="s">
+        <v>2</v>
+      </c>
+      <c r="C251" t="s">
+        <v>70</v>
+      </c>
+      <c r="D251">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B252" t="s">
+        <v>2</v>
+      </c>
+      <c r="C252" t="s">
+        <v>72</v>
+      </c>
+      <c r="D252">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B253" t="s">
+        <v>2</v>
+      </c>
+      <c r="C253" t="s">
+        <v>74</v>
+      </c>
+      <c r="D253">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B254" t="s">
+        <v>2</v>
+      </c>
+      <c r="C254" t="s">
+        <v>76</v>
+      </c>
+      <c r="D254">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B255" t="s">
+        <v>2</v>
+      </c>
+      <c r="C255" t="s">
+        <v>78</v>
+      </c>
+      <c r="D255">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B256" t="s">
+        <v>2</v>
+      </c>
+      <c r="C256" t="s">
+        <v>80</v>
+      </c>
+      <c r="D256">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B257" t="s">
+        <v>13</v>
+      </c>
+      <c r="C257" t="s">
+        <v>82</v>
+      </c>
+      <c r="D257">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B258" t="s">
+        <v>3</v>
+      </c>
+      <c r="C258" t="s">
+        <v>84</v>
+      </c>
+      <c r="D258">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B259" t="s">
+        <v>4</v>
+      </c>
+      <c r="C259" t="s">
+        <v>86</v>
+      </c>
+      <c r="D259">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B260" t="s">
+        <v>4</v>
+      </c>
+      <c r="C260" t="s">
+        <v>88</v>
+      </c>
+      <c r="D260">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B261" t="s">
+        <v>4</v>
+      </c>
+      <c r="C261" t="s">
+        <v>90</v>
+      </c>
+      <c r="D261">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B262" t="s">
+        <v>4</v>
+      </c>
+      <c r="C262" t="s">
+        <v>92</v>
+      </c>
+      <c r="D262">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B263" t="s">
+        <v>4</v>
+      </c>
+      <c r="C263" t="s">
+        <v>94</v>
+      </c>
+      <c r="D263">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B264" t="s">
+        <v>4</v>
+      </c>
+      <c r="C264" t="s">
+        <v>96</v>
+      </c>
+      <c r="D264">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B265" t="s">
+        <v>4</v>
+      </c>
+      <c r="C265" t="s">
+        <v>98</v>
+      </c>
+      <c r="D265">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B266" t="s">
+        <v>4</v>
+      </c>
+      <c r="C266" t="s">
+        <v>100</v>
+      </c>
+      <c r="D266">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B267" t="s">
+        <v>4</v>
+      </c>
+      <c r="C267" t="s">
+        <v>102</v>
+      </c>
+      <c r="D267">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B268" t="s">
+        <v>4</v>
+      </c>
+      <c r="C268" t="s">
+        <v>104</v>
+      </c>
+      <c r="D268">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B269" t="s">
+        <v>4</v>
+      </c>
+      <c r="C269" t="s">
+        <v>106</v>
+      </c>
+      <c r="D269">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B270" t="s">
+        <v>4</v>
+      </c>
+      <c r="C270" t="s">
+        <v>108</v>
+      </c>
+      <c r="D270">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B271" t="s">
+        <v>4</v>
+      </c>
+      <c r="C271" t="s">
+        <v>110</v>
+      </c>
+      <c r="D271">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B272" t="s">
+        <v>4</v>
+      </c>
+      <c r="C272" t="s">
+        <v>112</v>
+      </c>
+      <c r="D272">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B273" t="s">
+        <v>4</v>
+      </c>
+      <c r="C273" t="s">
+        <v>114</v>
+      </c>
+      <c r="D273">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B274" t="s">
+        <v>4</v>
+      </c>
+      <c r="C274" t="s">
+        <v>116</v>
+      </c>
+      <c r="D274">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B275" t="s">
+        <v>4</v>
+      </c>
+      <c r="C275" t="s">
+        <v>118</v>
+      </c>
+      <c r="D275">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B276" t="s">
+        <v>4</v>
+      </c>
+      <c r="C276" t="s">
+        <v>120</v>
+      </c>
+      <c r="D276">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B277" t="s">
+        <v>4</v>
+      </c>
+      <c r="C277" t="s">
+        <v>122</v>
+      </c>
+      <c r="D277">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B278" t="s">
+        <v>0</v>
+      </c>
+      <c r="C278" t="s">
+        <v>32</v>
+      </c>
+      <c r="D278">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B279" t="s">
+        <v>1</v>
+      </c>
+      <c r="C279" t="s">
+        <v>34</v>
+      </c>
+      <c r="D279">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B280" t="s">
+        <v>1</v>
+      </c>
+      <c r="C280" t="s">
+        <v>36</v>
+      </c>
+      <c r="D280">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B281" t="s">
+        <v>1</v>
+      </c>
+      <c r="C281" t="s">
+        <v>38</v>
+      </c>
+      <c r="D281">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B282" t="s">
+        <v>1</v>
+      </c>
+      <c r="C282" t="s">
+        <v>40</v>
+      </c>
+      <c r="D282">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B283" t="s">
+        <v>1</v>
+      </c>
+      <c r="C283" t="s">
+        <v>42</v>
+      </c>
+      <c r="D283">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B284" t="s">
+        <v>1</v>
+      </c>
+      <c r="C284" t="s">
+        <v>44</v>
+      </c>
+      <c r="D284">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1</v>
+      </c>
+      <c r="C285" t="s">
+        <v>46</v>
+      </c>
+      <c r="D285">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B286" t="s">
+        <v>1</v>
+      </c>
+      <c r="C286" t="s">
+        <v>48</v>
+      </c>
+      <c r="D286">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B287" t="s">
+        <v>1</v>
+      </c>
+      <c r="C287" t="s">
+        <v>50</v>
+      </c>
+      <c r="D287">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B288" t="s">
+        <v>2</v>
+      </c>
+      <c r="C288" t="s">
+        <v>52</v>
+      </c>
+      <c r="D288">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B289" t="s">
+        <v>2</v>
+      </c>
+      <c r="C289" t="s">
+        <v>54</v>
+      </c>
+      <c r="D289">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B290" t="s">
+        <v>2</v>
+      </c>
+      <c r="C290" t="s">
+        <v>56</v>
+      </c>
+      <c r="D290">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B291" t="s">
+        <v>2</v>
+      </c>
+      <c r="C291" t="s">
+        <v>58</v>
+      </c>
+      <c r="D291">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B292" t="s">
+        <v>2</v>
+      </c>
+      <c r="C292" t="s">
+        <v>60</v>
+      </c>
+      <c r="D292">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B293" t="s">
+        <v>2</v>
+      </c>
+      <c r="C293" t="s">
+        <v>62</v>
+      </c>
+      <c r="D293">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B294" t="s">
+        <v>2</v>
+      </c>
+      <c r="C294" t="s">
+        <v>64</v>
+      </c>
+      <c r="D294">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B295" t="s">
+        <v>2</v>
+      </c>
+      <c r="C295" t="s">
+        <v>66</v>
+      </c>
+      <c r="D295">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B296" t="s">
+        <v>2</v>
+      </c>
+      <c r="C296" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B297" t="s">
+        <v>2</v>
+      </c>
+      <c r="C297" t="s">
+        <v>70</v>
+      </c>
+      <c r="D297">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B298" t="s">
+        <v>2</v>
+      </c>
+      <c r="C298" t="s">
+        <v>72</v>
+      </c>
+      <c r="D298">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B299" t="s">
+        <v>2</v>
+      </c>
+      <c r="C299" t="s">
+        <v>74</v>
+      </c>
+      <c r="D299">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B300" t="s">
+        <v>2</v>
+      </c>
+      <c r="C300" t="s">
+        <v>76</v>
+      </c>
+      <c r="D300">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B301" t="s">
+        <v>2</v>
+      </c>
+      <c r="C301" t="s">
+        <v>78</v>
+      </c>
+      <c r="D301">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B302" t="s">
+        <v>2</v>
+      </c>
+      <c r="C302" t="s">
+        <v>80</v>
+      </c>
+      <c r="D302">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B303" t="s">
+        <v>13</v>
+      </c>
+      <c r="C303" t="s">
+        <v>82</v>
+      </c>
+      <c r="D303">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B304" t="s">
+        <v>3</v>
+      </c>
+      <c r="C304" t="s">
+        <v>84</v>
+      </c>
+      <c r="D304">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B305" t="s">
+        <v>4</v>
+      </c>
+      <c r="C305" t="s">
+        <v>86</v>
+      </c>
+      <c r="D305">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B306" t="s">
+        <v>4</v>
+      </c>
+      <c r="C306" t="s">
+        <v>88</v>
+      </c>
+      <c r="D306">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B307" t="s">
+        <v>4</v>
+      </c>
+      <c r="C307" t="s">
+        <v>90</v>
+      </c>
+      <c r="D307">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B308" t="s">
+        <v>4</v>
+      </c>
+      <c r="C308" t="s">
+        <v>92</v>
+      </c>
+      <c r="D308">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B309" t="s">
+        <v>4</v>
+      </c>
+      <c r="C309" t="s">
+        <v>94</v>
+      </c>
+      <c r="D309">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B310" t="s">
+        <v>4</v>
+      </c>
+      <c r="C310" t="s">
+        <v>96</v>
+      </c>
+      <c r="D310">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B311" t="s">
+        <v>4</v>
+      </c>
+      <c r="C311" t="s">
+        <v>98</v>
+      </c>
+      <c r="D311">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B312" t="s">
+        <v>4</v>
+      </c>
+      <c r="C312" t="s">
+        <v>100</v>
+      </c>
+      <c r="D312">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B313" t="s">
+        <v>4</v>
+      </c>
+      <c r="C313" t="s">
+        <v>102</v>
+      </c>
+      <c r="D313">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B314" t="s">
+        <v>4</v>
+      </c>
+      <c r="C314" t="s">
+        <v>104</v>
+      </c>
+      <c r="D314">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B315" t="s">
+        <v>4</v>
+      </c>
+      <c r="C315" t="s">
+        <v>106</v>
+      </c>
+      <c r="D315">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B316" t="s">
+        <v>4</v>
+      </c>
+      <c r="C316" t="s">
+        <v>108</v>
+      </c>
+      <c r="D316">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B317" t="s">
+        <v>4</v>
+      </c>
+      <c r="C317" t="s">
+        <v>110</v>
+      </c>
+      <c r="D317">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B318" t="s">
+        <v>4</v>
+      </c>
+      <c r="C318" t="s">
+        <v>112</v>
+      </c>
+      <c r="D318">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B319" t="s">
+        <v>4</v>
+      </c>
+      <c r="C319" t="s">
+        <v>114</v>
+      </c>
+      <c r="D319">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B320" t="s">
+        <v>4</v>
+      </c>
+      <c r="C320" t="s">
+        <v>116</v>
+      </c>
+      <c r="D320">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B321" t="s">
+        <v>4</v>
+      </c>
+      <c r="C321" t="s">
+        <v>118</v>
+      </c>
+      <c r="D321">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B322" t="s">
+        <v>4</v>
+      </c>
+      <c r="C322" t="s">
+        <v>120</v>
+      </c>
+      <c r="D322">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B323" t="s">
+        <v>4</v>
+      </c>
+      <c r="C323" t="s">
+        <v>122</v>
+      </c>
+      <c r="D323">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
